--- a/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
+++ b/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRIN 3219\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920925B8-1780-4AC1-9955-CEB06F2CB893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA8D697-425D-4595-8B90-2A352D9748AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
@@ -489,21 +489,6 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>VTO: 14/08</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - JULIO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - JULIO</t>
-  </si>
-  <si>
-    <t>Julio doartero - Emergencia caño pluvial sabotaje - 3 visitas</t>
-  </si>
-  <si>
     <t>Compra dispositivos para ahuyentar ratas -  Situacion en PB</t>
   </si>
   <si>
@@ -520,6 +505,21 @@
   </si>
   <si>
     <t>MATAFUEGOS PENDIENTES PARA AGOST000</t>
+  </si>
+  <si>
+    <t>VTO: 15/09</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - AGOSTO</t>
+  </si>
+  <si>
+    <t>AGOSTO doartero - Emergencia caño pluvial sabotaje - 3 visitas</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -527,16 +527,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,6 +741,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1318,18 +1333,18 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1338,16 +1353,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1362,7 +1377,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1372,10 +1387,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1404,13 +1419,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1422,38 +1437,38 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1461,24 +1476,24 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1513,50 +1528,50 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1564,8 +1579,8 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1575,9 +1590,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1585,48 +1600,49 @@
     <xf numFmtId="10" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1638,6 +1654,102 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1647,22 +1759,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1677,94 +1777,11 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2212,21 +2229,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2240,11 +2257,11 @@
       </c>
       <c r="F1" s="106" t="str">
         <f>RESUMEN!F8</f>
-        <v>JULIO</v>
+        <v>AGOSTO</v>
       </c>
       <c r="G1" s="107" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 14/08</v>
+        <v>VTO: 15/09</v>
       </c>
       <c r="H1" s="104"/>
       <c r="I1" s="104"/>
@@ -2316,11 +2333,11 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="121"/>
-      <c r="B5" s="185">
+      <c r="B5" s="186">
         <f>C3</f>
         <v>1886797.93</v>
       </c>
-      <c r="C5" s="185"/>
+      <c r="C5" s="186"/>
       <c r="D5" s="21"/>
       <c r="E5" s="122">
         <v>70000</v>
@@ -2357,10 +2374,10 @@
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
       <c r="A7" s="121"/>
-      <c r="B7" s="185">
+      <c r="B7" s="186">
         <v>1800000</v>
       </c>
-      <c r="C7" s="185"/>
+      <c r="C7" s="186"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="115"/>
@@ -3578,7 +3595,7 @@
         <v>152633.43430199998</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.75">
+    <row r="32" spans="1:15" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -3629,112 +3646,112 @@
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="184"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="K34" s="184"/>
-      <c r="L34" s="184"/>
-      <c r="M34" s="184"/>
-      <c r="N34" s="184"/>
+      <c r="B34" s="185"/>
+      <c r="C34" s="185"/>
+      <c r="D34" s="185"/>
+      <c r="E34" s="185"/>
+      <c r="F34" s="185"/>
+      <c r="G34" s="185"/>
+      <c r="H34" s="185"/>
+      <c r="I34" s="185"/>
+      <c r="J34" s="185"/>
+      <c r="K34" s="185"/>
+      <c r="L34" s="185"/>
+      <c r="M34" s="185"/>
+      <c r="N34" s="185"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="184"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-      <c r="M35" s="184"/>
-      <c r="N35" s="184"/>
+      <c r="B35" s="185"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="185"/>
+      <c r="G35" s="185"/>
+      <c r="H35" s="185"/>
+      <c r="I35" s="185"/>
+      <c r="J35" s="185"/>
+      <c r="K35" s="185"/>
+      <c r="L35" s="185"/>
+      <c r="M35" s="185"/>
+      <c r="N35" s="185"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="184"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-      <c r="M36" s="184"/>
-      <c r="N36" s="184"/>
+      <c r="B36" s="185"/>
+      <c r="C36" s="185"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="185"/>
+      <c r="H36" s="185"/>
+      <c r="I36" s="185"/>
+      <c r="J36" s="185"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="185"/>
+      <c r="M36" s="185"/>
+      <c r="N36" s="185"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="184"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-      <c r="M37" s="184"/>
-      <c r="N37" s="184"/>
+      <c r="B37" s="185"/>
+      <c r="C37" s="185"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="185"/>
+      <c r="F37" s="185"/>
+      <c r="G37" s="185"/>
+      <c r="H37" s="185"/>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
+      <c r="M37" s="185"/>
+      <c r="N37" s="185"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="186"/>
-      <c r="B38" s="186"/>
-      <c r="C38" s="186"/>
-      <c r="D38" s="186"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="186"/>
-      <c r="H38" s="186"/>
-      <c r="I38" s="186"/>
-      <c r="J38" s="186"/>
-      <c r="K38" s="186"/>
-      <c r="L38" s="186"/>
-      <c r="M38" s="186"/>
-      <c r="N38" s="186"/>
+      <c r="A38" s="187"/>
+      <c r="B38" s="187"/>
+      <c r="C38" s="187"/>
+      <c r="D38" s="187"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="187"/>
+      <c r="H38" s="187"/>
+      <c r="I38" s="187"/>
+      <c r="J38" s="187"/>
+      <c r="K38" s="187"/>
+      <c r="L38" s="187"/>
+      <c r="M38" s="187"/>
+      <c r="N38" s="187"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="186"/>
-      <c r="B39" s="186"/>
-      <c r="C39" s="186"/>
-      <c r="D39" s="186"/>
-      <c r="E39" s="186"/>
-      <c r="F39" s="186"/>
-      <c r="G39" s="186"/>
-      <c r="H39" s="186"/>
-      <c r="I39" s="186"/>
-      <c r="J39" s="186"/>
-      <c r="K39" s="186"/>
-      <c r="L39" s="186"/>
-      <c r="M39" s="186"/>
-      <c r="N39" s="186"/>
+      <c r="A39" s="187"/>
+      <c r="B39" s="187"/>
+      <c r="C39" s="187"/>
+      <c r="D39" s="187"/>
+      <c r="E39" s="187"/>
+      <c r="F39" s="187"/>
+      <c r="G39" s="187"/>
+      <c r="H39" s="187"/>
+      <c r="I39" s="187"/>
+      <c r="J39" s="187"/>
+      <c r="K39" s="187"/>
+      <c r="L39" s="187"/>
+      <c r="M39" s="187"/>
+      <c r="N39" s="187"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="186"/>
-      <c r="B40" s="186"/>
-      <c r="C40" s="186"/>
-      <c r="D40" s="186"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186"/>
-      <c r="G40" s="186"/>
-      <c r="H40" s="186"/>
-      <c r="I40" s="186"/>
-      <c r="J40" s="186"/>
-      <c r="K40" s="186"/>
-      <c r="L40" s="186"/>
-      <c r="M40" s="186"/>
-      <c r="N40" s="186"/>
+      <c r="A40" s="187"/>
+      <c r="B40" s="187"/>
+      <c r="C40" s="187"/>
+      <c r="D40" s="187"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="187"/>
+      <c r="H40" s="187"/>
+      <c r="I40" s="187"/>
+      <c r="J40" s="187"/>
+      <c r="K40" s="187"/>
+      <c r="L40" s="187"/>
+      <c r="M40" s="187"/>
+      <c r="N40" s="187"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -3755,25 +3772,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="188" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="189"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="190"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -3809,13 +3826,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+    <row r="7" spans="1:7" ht="15" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="30.75" thickBot="1">
+    <row r="8" spans="1:7" ht="29.4" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -4176,7 +4193,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75">
+    <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -4198,7 +4215,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
+    <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -4220,7 +4237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
+    <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -4242,7 +4259,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
+    <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -4268,7 +4285,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
+    <row r="28" spans="1:7" ht="15.6">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -4290,7 +4307,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
+    <row r="29" spans="1:7" ht="15.6">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -4312,7 +4329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.6">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -4334,7 +4351,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75">
+    <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -4356,7 +4373,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75">
+    <row r="32" spans="1:7" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -4397,16 +4414,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4421,23 +4438,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="192"/>
+      <c r="D2" s="223"/>
+      <c r="E2" s="224"/>
+      <c r="F2" s="224"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="224">
+      <c r="E3" s="199">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="224"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="225"/>
+      <c r="F3" s="199"/>
+      <c r="G3" s="199"/>
+      <c r="H3" s="200"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -4473,7 +4490,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -4484,10 +4501,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -4516,14 +4533,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="202"/>
-      <c r="B12" s="203"/>
-      <c r="C12" s="203"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="203"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="204"/>
+      <c r="A12" s="231"/>
+      <c r="B12" s="192"/>
+      <c r="C12" s="192"/>
+      <c r="D12" s="192"/>
+      <c r="E12" s="192"/>
+      <c r="F12" s="192"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="232"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -4535,21 +4552,21 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="228" t="s">
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="205" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="228"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="228"/>
-      <c r="E14" s="228"/>
-      <c r="F14" s="228"/>
-      <c r="G14" s="228"/>
-      <c r="H14" s="228"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="205"/>
+      <c r="H14" s="205"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="170" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B15" s="141"/>
       <c r="C15" s="141"/>
@@ -4608,16 +4625,16 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="198" t="s">
+      <c r="A19" s="227" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="198"/>
-      <c r="C19" s="198"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="198"/>
+      <c r="B19" s="227"/>
+      <c r="C19" s="227"/>
+      <c r="D19" s="227"/>
+      <c r="E19" s="227"/>
+      <c r="F19" s="227"/>
+      <c r="G19" s="227"/>
+      <c r="H19" s="227"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="170" t="s">
@@ -4707,16 +4724,16 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="197" t="s">
+      <c r="A27" s="226" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="197"/>
-      <c r="C27" s="197"/>
-      <c r="D27" s="197"/>
-      <c r="E27" s="197"/>
-      <c r="F27" s="197"/>
-      <c r="G27" s="197"/>
-      <c r="H27" s="197"/>
+      <c r="B27" s="226"/>
+      <c r="C27" s="226"/>
+      <c r="D27" s="226"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="226"/>
+      <c r="G27" s="226"/>
+      <c r="H27" s="226"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="141" t="s">
@@ -4758,16 +4775,16 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="193" t="s">
+      <c r="A31" s="206" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="193"/>
-      <c r="C31" s="193"/>
-      <c r="D31" s="193"/>
-      <c r="E31" s="193"/>
-      <c r="F31" s="193"/>
-      <c r="G31" s="193"/>
-      <c r="H31" s="193"/>
+      <c r="B31" s="206"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="206"/>
+      <c r="E31" s="206"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="206"/>
     </row>
     <row r="32" spans="1:9" hidden="1">
       <c r="A32" s="170"/>
@@ -4789,9 +4806,9 @@
       <c r="E33" s="141"/>
       <c r="F33" s="141"/>
       <c r="G33" s="141"/>
-      <c r="H33" s="74">
-        <f>43621.94+1955.69+17601.19</f>
-        <v>63178.820000000007</v>
+      <c r="H33" s="233">
+        <f>43594.41+2406.19+31655.67</f>
+        <v>77656.27</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -4820,24 +4837,24 @@
       <c r="G35" s="141"/>
       <c r="H35" s="74">
         <f>SUM(H32:H34)</f>
-        <v>63178.820000000007</v>
+        <v>77656.27</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="193" t="s">
+      <c r="A36" s="206" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="193"/>
-      <c r="C36" s="193"/>
-      <c r="D36" s="193"/>
-      <c r="E36" s="193"/>
-      <c r="F36" s="193"/>
-      <c r="G36" s="193"/>
-      <c r="H36" s="193"/>
+      <c r="B36" s="206"/>
+      <c r="C36" s="206"/>
+      <c r="D36" s="206"/>
+      <c r="E36" s="206"/>
+      <c r="F36" s="206"/>
+      <c r="G36" s="206"/>
+      <c r="H36" s="206"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1">
       <c r="A37" s="141" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B37" s="141"/>
       <c r="C37" s="141"/>
@@ -4845,13 +4862,13 @@
       <c r="E37" s="141"/>
       <c r="F37" s="141"/>
       <c r="G37" s="141"/>
-      <c r="H37" s="74">
-        <v>1057899.3600000001</v>
+      <c r="H37" s="233">
+        <v>2015397.65</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="14.25" customHeight="1">
       <c r="A38" s="141" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B38" s="141"/>
       <c r="C38" s="141"/>
@@ -4873,8 +4890,8 @@
       <c r="E39" s="141"/>
       <c r="F39" s="141"/>
       <c r="G39" s="141"/>
-      <c r="H39" s="74">
-        <v>60230.82</v>
+      <c r="H39" s="233">
+        <v>63551.040000000001</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -4889,20 +4906,20 @@
       <c r="G40" s="141"/>
       <c r="H40" s="145">
         <f>SUM(H37:H39)</f>
-        <v>2174431.15</v>
+        <v>3135249.66</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="228" t="s">
+      <c r="A41" s="205" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="228"/>
-      <c r="C41" s="228"/>
-      <c r="D41" s="228"/>
-      <c r="E41" s="228"/>
-      <c r="F41" s="228"/>
-      <c r="G41" s="228"/>
-      <c r="H41" s="228"/>
+      <c r="B41" s="205"/>
+      <c r="C41" s="205"/>
+      <c r="D41" s="205"/>
+      <c r="E41" s="205"/>
+      <c r="F41" s="205"/>
+      <c r="G41" s="205"/>
+      <c r="H41" s="205"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="81" t="s">
@@ -4914,8 +4931,8 @@
       <c r="E42" s="141"/>
       <c r="F42" s="141"/>
       <c r="G42" s="141"/>
-      <c r="H42" s="74">
-        <v>56500</v>
+      <c r="H42" s="233">
+        <v>64500</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -4928,13 +4945,13 @@
       <c r="E43" s="141"/>
       <c r="F43" s="141"/>
       <c r="G43" s="141"/>
-      <c r="H43" s="74">
-        <v>19610</v>
+      <c r="H43" s="233">
+        <v>19950.189999999999</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="81" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B44" s="81"/>
       <c r="C44" s="81"/>
@@ -4948,7 +4965,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="141" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B45" s="141"/>
       <c r="C45" s="141"/>
@@ -4970,16 +4987,16 @@
       <c r="E46" s="141"/>
       <c r="F46" s="141"/>
       <c r="G46" s="141"/>
-      <c r="H46" s="74">
-        <v>51490</v>
-      </c>
-      <c r="J46" s="232" t="s">
-        <v>158</v>
+      <c r="H46" s="233">
+        <v>35250</v>
+      </c>
+      <c r="J46" s="184" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="81" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B47" s="141"/>
       <c r="C47" s="141"/>
@@ -5002,20 +5019,20 @@
       <c r="G48" s="141"/>
       <c r="H48" s="70">
         <f>SUM(H42:H47)</f>
-        <v>492600</v>
+        <v>484700.19</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="228" t="s">
+      <c r="A49" s="205" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="228"/>
-      <c r="C49" s="228"/>
-      <c r="D49" s="228"/>
-      <c r="E49" s="228"/>
-      <c r="F49" s="228"/>
-      <c r="G49" s="228"/>
-      <c r="H49" s="228"/>
+      <c r="B49" s="205"/>
+      <c r="C49" s="205"/>
+      <c r="D49" s="205"/>
+      <c r="E49" s="205"/>
+      <c r="F49" s="205"/>
+      <c r="G49" s="205"/>
+      <c r="H49" s="205"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="141" t="s">
@@ -5031,7 +5048,7 @@
         <v>148100</v>
       </c>
       <c r="J50" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5075,16 +5092,16 @@
       <c r="K53" s="7"/>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="229" t="s">
+      <c r="A54" s="207" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="230"/>
-      <c r="C54" s="230"/>
-      <c r="D54" s="230"/>
-      <c r="E54" s="230"/>
-      <c r="F54" s="230"/>
-      <c r="G54" s="230"/>
-      <c r="H54" s="231"/>
+      <c r="B54" s="208"/>
+      <c r="C54" s="208"/>
+      <c r="D54" s="208"/>
+      <c r="E54" s="208"/>
+      <c r="F54" s="208"/>
+      <c r="G54" s="208"/>
+      <c r="H54" s="209"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
       <c r="A55" s="81" t="s">
@@ -5096,7 +5113,7 @@
       <c r="E55" s="81"/>
       <c r="F55" s="81"/>
       <c r="G55" s="81"/>
-      <c r="H55" s="70">
+      <c r="H55" s="234">
         <v>23006</v>
       </c>
       <c r="I55" s="60"/>
@@ -5117,16 +5134,16 @@
       </c>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="228" t="s">
+      <c r="A57" s="205" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="228"/>
-      <c r="C57" s="228"/>
-      <c r="D57" s="228"/>
-      <c r="E57" s="228"/>
-      <c r="F57" s="228"/>
-      <c r="G57" s="228"/>
-      <c r="H57" s="228"/>
+      <c r="B57" s="205"/>
+      <c r="C57" s="205"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="205"/>
+      <c r="F57" s="205"/>
+      <c r="G57" s="205"/>
+      <c r="H57" s="205"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
       <c r="A58" s="81"/>
@@ -5177,14 +5194,14 @@
       <c r="I61" s="60"/>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="229"/>
-      <c r="B62" s="230"/>
-      <c r="C62" s="230"/>
-      <c r="D62" s="230"/>
-      <c r="E62" s="230"/>
-      <c r="F62" s="230"/>
-      <c r="G62" s="230"/>
-      <c r="H62" s="231"/>
+      <c r="A62" s="207"/>
+      <c r="B62" s="208"/>
+      <c r="C62" s="208"/>
+      <c r="D62" s="208"/>
+      <c r="E62" s="208"/>
+      <c r="F62" s="208"/>
+      <c r="G62" s="208"/>
+      <c r="H62" s="209"/>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A63" s="82"/>
@@ -5224,60 +5241,60 @@
       </c>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A66" s="210" t="s">
+      <c r="A66" s="218" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="211"/>
-      <c r="C66" s="211"/>
-      <c r="D66" s="211"/>
-      <c r="E66" s="211"/>
-      <c r="F66" s="211"/>
-      <c r="G66" s="211"/>
+      <c r="B66" s="219"/>
+      <c r="C66" s="219"/>
+      <c r="D66" s="219"/>
+      <c r="E66" s="219"/>
+      <c r="F66" s="219"/>
+      <c r="G66" s="219"/>
       <c r="H66" s="168">
         <f>H61</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A67" s="215"/>
-      <c r="B67" s="215"/>
-      <c r="C67" s="215"/>
-      <c r="D67" s="215"/>
-      <c r="E67" s="215"/>
-      <c r="F67" s="215"/>
-      <c r="G67" s="215"/>
-      <c r="H67" s="215"/>
+      <c r="A67" s="221"/>
+      <c r="B67" s="221"/>
+      <c r="C67" s="221"/>
+      <c r="D67" s="221"/>
+      <c r="E67" s="221"/>
+      <c r="F67" s="221"/>
+      <c r="G67" s="221"/>
+      <c r="H67" s="221"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A68" s="216"/>
-      <c r="B68" s="216"/>
-      <c r="C68" s="216"/>
-      <c r="D68" s="216"/>
-      <c r="E68" s="216"/>
-      <c r="F68" s="216"/>
-      <c r="G68" s="216"/>
-      <c r="H68" s="216"/>
+      <c r="A68" s="222"/>
+      <c r="B68" s="222"/>
+      <c r="C68" s="222"/>
+      <c r="D68" s="222"/>
+      <c r="E68" s="222"/>
+      <c r="F68" s="222"/>
+      <c r="G68" s="222"/>
+      <c r="H68" s="222"/>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A69" s="214" t="s">
+      <c r="A69" s="220" t="s">
         <v>86</v>
       </c>
-      <c r="B69" s="214"/>
-      <c r="C69" s="214"/>
-      <c r="D69" s="214"/>
-      <c r="E69" s="214"/>
-      <c r="F69" s="214"/>
-      <c r="G69" s="214"/>
+      <c r="B69" s="220"/>
+      <c r="C69" s="220"/>
+      <c r="D69" s="220"/>
+      <c r="E69" s="220"/>
+      <c r="F69" s="220"/>
+      <c r="G69" s="220"/>
       <c r="H69" s="169"/>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A70" s="199"/>
-      <c r="B70" s="200"/>
-      <c r="C70" s="200"/>
-      <c r="D70" s="200"/>
-      <c r="E70" s="200"/>
-      <c r="F70" s="200"/>
-      <c r="G70" s="201"/>
+      <c r="A70" s="228"/>
+      <c r="B70" s="229"/>
+      <c r="C70" s="229"/>
+      <c r="D70" s="229"/>
+      <c r="E70" s="229"/>
+      <c r="F70" s="229"/>
+      <c r="G70" s="230"/>
       <c r="H70" s="74"/>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
@@ -5306,91 +5323,91 @@
       <c r="H72" s="133"/>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="212" t="s">
+      <c r="A73" s="201" t="s">
         <v>85</v>
       </c>
-      <c r="B73" s="213"/>
-      <c r="C73" s="213"/>
-      <c r="D73" s="213"/>
-      <c r="E73" s="213"/>
-      <c r="F73" s="213"/>
-      <c r="G73" s="213"/>
+      <c r="B73" s="202"/>
+      <c r="C73" s="202"/>
+      <c r="D73" s="202"/>
+      <c r="E73" s="202"/>
+      <c r="F73" s="202"/>
+      <c r="G73" s="202"/>
       <c r="H73" s="134">
         <f>H71</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A74" s="194" t="s">
+      <c r="A74" s="213" t="s">
         <v>91</v>
       </c>
-      <c r="B74" s="195"/>
-      <c r="C74" s="195"/>
-      <c r="D74" s="195"/>
-      <c r="E74" s="195"/>
-      <c r="F74" s="195"/>
-      <c r="G74" s="196"/>
+      <c r="B74" s="214"/>
+      <c r="C74" s="214"/>
+      <c r="D74" s="214"/>
+      <c r="E74" s="214"/>
+      <c r="F74" s="214"/>
+      <c r="G74" s="215"/>
       <c r="H74" s="134"/>
     </row>
     <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="194" t="s">
+      <c r="A75" s="213" t="s">
         <v>96</v>
       </c>
-      <c r="B75" s="195"/>
-      <c r="C75" s="195"/>
-      <c r="D75" s="195"/>
-      <c r="E75" s="195"/>
-      <c r="F75" s="195"/>
-      <c r="G75" s="196"/>
+      <c r="B75" s="214"/>
+      <c r="C75" s="214"/>
+      <c r="D75" s="214"/>
+      <c r="E75" s="214"/>
+      <c r="F75" s="214"/>
+      <c r="G75" s="215"/>
       <c r="H75" s="134">
         <v>1800000</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="18.75">
-      <c r="A76" s="212" t="s">
+    <row r="76" spans="1:11" ht="18">
+      <c r="A76" s="201" t="s">
         <v>92</v>
       </c>
-      <c r="B76" s="213"/>
-      <c r="C76" s="213"/>
-      <c r="D76" s="213"/>
-      <c r="E76" s="213"/>
-      <c r="F76" s="213"/>
-      <c r="G76" s="213"/>
+      <c r="B76" s="202"/>
+      <c r="C76" s="202"/>
+      <c r="D76" s="202"/>
+      <c r="E76" s="202"/>
+      <c r="F76" s="202"/>
+      <c r="G76" s="202"/>
       <c r="H76" s="134">
         <f>H30+H40+H48+H53+H56+H35+H18+H26</f>
-        <v>3368758.9699999997</v>
+        <v>4336155.12</v>
       </c>
       <c r="J76" s="183"/>
       <c r="K76" s="146"/>
     </row>
-    <row r="77" spans="1:11" ht="18.75">
-      <c r="A77" s="205" t="s">
+    <row r="77" spans="1:11" ht="18">
+      <c r="A77" s="210" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="206"/>
-      <c r="C77" s="206"/>
-      <c r="D77" s="206"/>
-      <c r="E77" s="206"/>
-      <c r="F77" s="206"/>
-      <c r="G77" s="207"/>
+      <c r="B77" s="211"/>
+      <c r="C77" s="211"/>
+      <c r="D77" s="211"/>
+      <c r="E77" s="211"/>
+      <c r="F77" s="211"/>
+      <c r="G77" s="212"/>
       <c r="H77" s="135">
         <f>H74+H76</f>
-        <v>3368758.9699999997</v>
+        <v>4336155.12</v>
       </c>
       <c r="I77" s="130"/>
-      <c r="J77" s="217"/>
-      <c r="K77" s="217"/>
-    </row>
-    <row r="78" spans="1:11" ht="18.75">
-      <c r="A78" s="205" t="s">
+      <c r="J77" s="191"/>
+      <c r="K77" s="191"/>
+    </row>
+    <row r="78" spans="1:11" ht="18">
+      <c r="A78" s="210" t="s">
         <v>97</v>
       </c>
-      <c r="B78" s="206"/>
-      <c r="C78" s="206"/>
-      <c r="D78" s="206"/>
-      <c r="E78" s="206"/>
-      <c r="F78" s="206"/>
-      <c r="G78" s="207"/>
+      <c r="B78" s="211"/>
+      <c r="C78" s="211"/>
+      <c r="D78" s="211"/>
+      <c r="E78" s="211"/>
+      <c r="F78" s="211"/>
+      <c r="G78" s="212"/>
       <c r="H78" s="136">
         <f>H75+H73</f>
         <v>1800000</v>
@@ -5398,38 +5415,38 @@
       <c r="J78" s="146"/>
     </row>
     <row r="79" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A79" s="208" t="s">
+      <c r="A79" s="216" t="s">
         <v>87</v>
       </c>
-      <c r="B79" s="209"/>
-      <c r="C79" s="209"/>
-      <c r="D79" s="209"/>
-      <c r="E79" s="209"/>
-      <c r="F79" s="209"/>
-      <c r="G79" s="209"/>
+      <c r="B79" s="217"/>
+      <c r="C79" s="217"/>
+      <c r="D79" s="217"/>
+      <c r="E79" s="217"/>
+      <c r="F79" s="217"/>
+      <c r="G79" s="217"/>
       <c r="H79" s="137">
         <f>H76+H73</f>
-        <v>3368758.9699999997</v>
+        <v>4336155.12</v>
       </c>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="18.75" hidden="1">
-      <c r="A80" s="226" t="s">
+    <row r="80" spans="1:11" ht="18" hidden="1">
+      <c r="A80" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="B80" s="227"/>
-      <c r="C80" s="227"/>
-      <c r="D80" s="227"/>
-      <c r="E80" s="227"/>
-      <c r="F80" s="227"/>
-      <c r="G80" s="227"/>
+      <c r="B80" s="204"/>
+      <c r="C80" s="204"/>
+      <c r="D80" s="204"/>
+      <c r="E80" s="204"/>
+      <c r="F80" s="204"/>
+      <c r="G80" s="204"/>
       <c r="H80" s="138">
         <f>H65</f>
         <v>0</v>
       </c>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:11" ht="18.75" hidden="1">
+    <row r="81" spans="1:11" ht="18" hidden="1">
       <c r="A81" s="139"/>
       <c r="B81" s="139"/>
       <c r="C81" s="139"/>
@@ -5440,7 +5457,7 @@
       <c r="H81" s="140"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:11" ht="18.75" hidden="1">
+    <row r="82" spans="1:11" ht="18" hidden="1">
       <c r="A82" s="139"/>
       <c r="B82" s="139"/>
       <c r="C82" s="139"/>
@@ -5451,7 +5468,7 @@
       <c r="H82" s="140"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="18.75" hidden="1">
+    <row r="83" spans="1:11" ht="18" hidden="1">
       <c r="A83" s="139"/>
       <c r="B83" s="139"/>
       <c r="C83" s="139"/>
@@ -5472,19 +5489,19 @@
       <c r="G84" s="141"/>
       <c r="H84" s="141"/>
     </row>
-    <row r="85" spans="1:11" ht="18.75">
-      <c r="A85" s="221" t="s">
+    <row r="85" spans="1:11" ht="18">
+      <c r="A85" s="196" t="s">
         <v>10</v>
       </c>
-      <c r="B85" s="222"/>
-      <c r="C85" s="222"/>
-      <c r="D85" s="222"/>
-      <c r="E85" s="222"/>
-      <c r="F85" s="222"/>
-      <c r="G85" s="222"/>
-      <c r="H85" s="223"/>
-    </row>
-    <row r="86" spans="1:11" ht="18.75">
+      <c r="B85" s="197"/>
+      <c r="C85" s="197"/>
+      <c r="D85" s="197"/>
+      <c r="E85" s="197"/>
+      <c r="F85" s="197"/>
+      <c r="G85" s="197"/>
+      <c r="H85" s="198"/>
+    </row>
+    <row r="86" spans="1:11" ht="18">
       <c r="A86" s="142" t="s">
         <v>12</v>
       </c>
@@ -5515,7 +5532,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="79" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B88" s="80"/>
       <c r="C88" s="80"/>
@@ -5525,7 +5542,7 @@
       <c r="G88" s="80"/>
       <c r="H88" s="69">
         <f>-(H79)</f>
-        <v>-3368758.9699999997</v>
+        <v>-4336155.12</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5590,7 +5607,7 @@
         <v>-5402</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="18.75">
+    <row r="93" spans="1:11" ht="18">
       <c r="A93" s="22" t="s">
         <v>11</v>
       </c>
@@ -5602,23 +5619,23 @@
       <c r="G93" s="23"/>
       <c r="H93" s="85">
         <f>SUM(H86:H92)</f>
-        <v>4747227.3433483643</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="95" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A95" s="218" t="s">
+        <v>3779831.193348364</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="15" thickBot="1"/>
+    <row r="95" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A95" s="193" t="s">
         <v>101</v>
       </c>
-      <c r="B95" s="219"/>
-      <c r="C95" s="219"/>
-      <c r="D95" s="219"/>
-      <c r="E95" s="219"/>
-      <c r="F95" s="219"/>
-      <c r="G95" s="219"/>
-      <c r="H95" s="220"/>
-    </row>
-    <row r="96" spans="1:11" ht="15.75">
+      <c r="B95" s="194"/>
+      <c r="C95" s="194"/>
+      <c r="D95" s="194"/>
+      <c r="E95" s="194"/>
+      <c r="F95" s="194"/>
+      <c r="G95" s="194"/>
+      <c r="H95" s="195"/>
+    </row>
+    <row r="96" spans="1:11" ht="15.6">
       <c r="A96" s="88" t="s">
         <v>12</v>
       </c>
@@ -5680,47 +5697,60 @@
       </c>
     </row>
     <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="203"/>
-      <c r="B103" s="203"/>
-      <c r="C103" s="203"/>
-      <c r="D103" s="203"/>
-      <c r="E103" s="203"/>
-      <c r="F103" s="203"/>
-      <c r="G103" s="203"/>
-      <c r="H103" s="203"/>
+      <c r="A103" s="192"/>
+      <c r="B103" s="192"/>
+      <c r="C103" s="192"/>
+      <c r="D103" s="192"/>
+      <c r="E103" s="192"/>
+      <c r="F103" s="192"/>
+      <c r="G103" s="192"/>
+      <c r="H103" s="192"/>
     </row>
     <row r="104" spans="1:8" hidden="1">
-      <c r="A104" s="203"/>
-      <c r="B104" s="203"/>
-      <c r="C104" s="203"/>
-      <c r="D104" s="203"/>
-      <c r="E104" s="203"/>
-      <c r="F104" s="203"/>
-      <c r="G104" s="203"/>
-      <c r="H104" s="203"/>
+      <c r="A104" s="192"/>
+      <c r="B104" s="192"/>
+      <c r="C104" s="192"/>
+      <c r="D104" s="192"/>
+      <c r="E104" s="192"/>
+      <c r="F104" s="192"/>
+      <c r="G104" s="192"/>
+      <c r="H104" s="192"/>
     </row>
     <row r="105" spans="1:8" hidden="1">
-      <c r="A105" s="203"/>
-      <c r="B105" s="203"/>
-      <c r="C105" s="203"/>
-      <c r="D105" s="203"/>
-      <c r="E105" s="203"/>
-      <c r="F105" s="203"/>
-      <c r="G105" s="203"/>
-      <c r="H105" s="203"/>
+      <c r="A105" s="192"/>
+      <c r="B105" s="192"/>
+      <c r="C105" s="192"/>
+      <c r="D105" s="192"/>
+      <c r="E105" s="192"/>
+      <c r="F105" s="192"/>
+      <c r="G105" s="192"/>
+      <c r="H105" s="192"/>
     </row>
     <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="203"/>
-      <c r="B106" s="203"/>
-      <c r="C106" s="203"/>
-      <c r="D106" s="203"/>
-      <c r="E106" s="203"/>
-      <c r="F106" s="203"/>
-      <c r="G106" s="203"/>
-      <c r="H106" s="203"/>
+      <c r="A106" s="192"/>
+      <c r="B106" s="192"/>
+      <c r="C106" s="192"/>
+      <c r="D106" s="192"/>
+      <c r="E106" s="192"/>
+      <c r="F106" s="192"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="192"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A67:H68"/>
     <mergeCell ref="J77:K77"/>
     <mergeCell ref="A103:H106"/>
     <mergeCell ref="A95:H95"/>
@@ -5737,19 +5767,6 @@
     <mergeCell ref="A62:H62"/>
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A67:H68"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>

--- a/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
+++ b/BRIN 3219/Agosto/BRIN3219-EXPENSAS-Agosto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRIN 3219\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA8D697-425D-4595-8B90-2A352D9748AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8006AADD-E11B-43E7-B15F-DB5B2D70886A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="158">
   <si>
     <t>U.F.</t>
   </si>
@@ -489,24 +489,12 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Compra dispositivos para ahuyentar ratas -  Situacion en PB</t>
-  </si>
-  <si>
-    <t>AYSA - 11/07 - VTO. 30/06</t>
-  </si>
-  <si>
-    <t>AYSA - 27/07 - VTO. 28/07</t>
-  </si>
-  <si>
     <t>subidos en juli</t>
   </si>
   <si>
     <t xml:space="preserve">Sueldo Sra Monica Forment </t>
   </si>
   <si>
-    <t>MATAFUEGOS PENDIENTES PARA AGOST000</t>
-  </si>
-  <si>
     <t>VTO: 15/09</t>
   </si>
   <si>
@@ -516,10 +504,19 @@
     <t>Damato fumigaciones - AGOSTO</t>
   </si>
   <si>
-    <t>AGOSTO doartero - Emergencia caño pluvial sabotaje - 3 visitas</t>
-  </si>
-  <si>
     <t>Egresos por gastos mes - AGOSTO</t>
+  </si>
+  <si>
+    <t>AYSA</t>
+  </si>
+  <si>
+    <t>Destapacion cloacal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Megasec Recarga de matafuegos </t>
+  </si>
+  <si>
+    <t>Dr. Sarro Murillo escrito</t>
   </si>
 </sst>
 </file>
@@ -527,16 +524,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -741,21 +738,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1333,18 +1315,18 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1353,16 +1335,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1377,7 +1359,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1387,10 +1369,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1419,13 +1401,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1437,38 +1419,38 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1476,24 +1458,24 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1528,50 +1510,50 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1579,8 +1561,8 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1590,9 +1572,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1600,49 +1582,38 @@
     <xf numFmtId="10" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1654,12 +1625,81 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1684,12 +1724,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1699,9 +1733,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1711,77 +1742,40 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2229,21 +2223,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2293,7 +2287,7 @@
       <c r="A3" s="116"/>
       <c r="B3" s="117"/>
       <c r="C3" s="102">
-        <v>1886797.93</v>
+        <v>3130261.15</v>
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
@@ -2319,7 +2313,10 @@
       <c r="E4" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="124"/>
+      <c r="F4" s="124">
+        <f>-107+95200-6</f>
+        <v>95087</v>
+      </c>
       <c r="G4" s="118"/>
       <c r="H4" s="118"/>
       <c r="I4" s="118"/>
@@ -2333,11 +2330,11 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="121"/>
-      <c r="B5" s="186">
+      <c r="B5" s="177">
         <f>C3</f>
-        <v>1886797.93</v>
-      </c>
-      <c r="C5" s="186"/>
+        <v>3130261.15</v>
+      </c>
+      <c r="C5" s="177"/>
       <c r="D5" s="21"/>
       <c r="E5" s="122">
         <v>70000</v>
@@ -2374,10 +2371,8 @@
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
       <c r="A7" s="121"/>
-      <c r="B7" s="186">
-        <v>1800000</v>
-      </c>
-      <c r="C7" s="186"/>
+      <c r="B7" s="177"/>
+      <c r="C7" s="177"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="115"/>
@@ -2435,32 +2430,32 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
-      <c r="A9" s="179">
+      <c r="A9" s="173">
         <v>1</v>
       </c>
-      <c r="B9" s="175" t="s">
+      <c r="B9" s="169" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="176" t="s">
+      <c r="C9" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="176" t="s">
+      <c r="D9" s="170" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="177">
+      <c r="E9" s="171">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="99">
-        <v>149315.316165</v>
-      </c>
-      <c r="G9" s="180"/>
+        <v>304155.29902810499</v>
+      </c>
+      <c r="G9" s="221"/>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>149315.316165</v>
+        <v>304155.29902810499</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>5524.6666981050003</v>
+        <v>11253.746064039886</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
@@ -2468,19 +2463,19 @@
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="178">
+        <v>3851.0235000000002</v>
+      </c>
+      <c r="L9" s="172">
         <f>B$5*E9</f>
-        <v>76415.316164999997</v>
-      </c>
-      <c r="M9" s="178">
+        <v>126775.576575</v>
+      </c>
+      <c r="M9" s="172">
         <f>B$7*E9</f>
-        <v>72900</v>
-      </c>
-      <c r="N9" s="178">
+        <v>0</v>
+      </c>
+      <c r="N9" s="172">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>304155.29902810499</v>
+        <v>446035.64516714489</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -2500,7 +2495,7 @@
       <c r="F10" s="17">
         <v>238904.50586400001</v>
       </c>
-      <c r="G10" s="160">
+      <c r="G10" s="222">
         <f>F10</f>
         <v>238904.50586400001</v>
       </c>
@@ -2518,41 +2513,41 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>0</v>
+        <v>6161.6376</v>
       </c>
       <c r="L10" s="25">
         <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
-        <v>122264.50586399999</v>
+        <v>202840.92251999999</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$7*E10</f>
-        <v>116640</v>
+        <v>0</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>238904.50586400001</v>
+        <v>209002.56011999998</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
-      <c r="A11" s="174">
+      <c r="A11" s="168">
         <v>3</v>
       </c>
-      <c r="B11" s="175" t="s">
+      <c r="B11" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="176" t="s">
+      <c r="C11" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="176" t="s">
+      <c r="D11" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="177">
+      <c r="E11" s="171">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="99">
         <v>177703.66022600001</v>
       </c>
-      <c r="G11" s="160">
+      <c r="G11" s="222">
         <f>F11</f>
         <v>177703.66022600001</v>
       </c>
@@ -2570,19 +2565,19 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="178">
+        <v>4583.1934000000001</v>
+      </c>
+      <c r="L11" s="172">
         <f t="shared" si="3"/>
-        <v>90943.660225999993</v>
-      </c>
-      <c r="M11" s="178">
+        <v>150878.58742999999</v>
+      </c>
+      <c r="M11" s="172">
         <f t="shared" si="4"/>
-        <v>86760</v>
-      </c>
-      <c r="N11" s="178">
+        <v>0</v>
+      </c>
+      <c r="N11" s="172">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>177703.66022600001</v>
+        <v>155461.78082999997</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
@@ -2602,16 +2597,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="151">
-        <v>1830207.2469590595</v>
-      </c>
-      <c r="G12" s="161"/>
+        <v>2095168.6043515448</v>
+      </c>
+      <c r="G12" s="223"/>
       <c r="H12" s="152">
         <f t="shared" si="0"/>
-        <v>1830207.2469590595</v>
+        <v>2095168.6043515448</v>
       </c>
       <c r="I12" s="152">
         <f t="shared" si="6"/>
-        <v>67717.668137485205</v>
+        <v>77521.23836100717</v>
       </c>
       <c r="J12" s="152">
         <f t="shared" si="1"/>
@@ -2619,19 +2614,19 @@
       </c>
       <c r="K12" s="152">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5087.1544999999996</v>
       </c>
       <c r="L12" s="153">
         <f t="shared" si="3"/>
-        <v>100943.68925499999</v>
+        <v>167468.971525</v>
       </c>
       <c r="M12" s="153">
         <f t="shared" si="4"/>
-        <v>96300</v>
+        <v>0</v>
       </c>
       <c r="N12" s="153">
         <f t="shared" si="5"/>
-        <v>2095168.6043515448</v>
+        <v>2345245.9687375519</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -2649,11 +2644,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>293353.38753528497</v>
-      </c>
-      <c r="G13" s="160">
+        <v>141941.720305</v>
+      </c>
+      <c r="G13" s="222">
         <f>F13</f>
-        <v>293353.38753528497</v>
+        <v>141941.720305</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -2669,19 +2664,19 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3660.8494999999998</v>
       </c>
       <c r="L13" s="25">
         <f t="shared" si="3"/>
-        <v>72641.720304999995</v>
+        <v>120515.05427499999</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -2703,7 +2698,7 @@
       <c r="F14" s="17">
         <v>132356.04568700001</v>
       </c>
-      <c r="G14" s="160">
+      <c r="G14" s="222">
         <f>F14</f>
         <v>132356.04568700001</v>
       </c>
@@ -2721,19 +2716,19 @@
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3413.6233000000002</v>
       </c>
       <c r="L14" s="25">
         <f t="shared" si="3"/>
-        <v>67736.045687000005</v>
+        <v>112376.375285</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>64620</v>
+        <v>0</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -2753,11 +2748,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>152649.12308202463</v>
-      </c>
-      <c r="G15" s="160">
+        <v>152633.43430199998</v>
+      </c>
+      <c r="G15" s="222">
         <f>F15</f>
-        <v>152649.12308202463</v>
+        <v>152633.43430199998</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -2773,19 +2768,19 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3936.6017999999999</v>
       </c>
       <c r="L15" s="25">
         <f t="shared" si="3"/>
-        <v>78113.434301999994</v>
+        <v>129592.81160999999</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>74520</v>
+        <v>0</v>
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>152633.43430199998</v>
+        <v>133529.41340999998</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -2807,7 +2802,7 @@
       <c r="F16" s="17">
         <v>197243.68925499998</v>
       </c>
-      <c r="G16" s="160">
+      <c r="G16" s="222">
         <f>F16</f>
         <v>197243.68925499998</v>
       </c>
@@ -2825,19 +2820,19 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5087.1544999999996</v>
       </c>
       <c r="L16" s="25">
         <f t="shared" si="3"/>
-        <v>100943.68925499999</v>
+        <v>167468.971525</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>96300</v>
+        <v>0</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1">
@@ -2859,7 +2854,7 @@
       <c r="F17" s="17">
         <v>141941.720305</v>
       </c>
-      <c r="G17" s="160">
+      <c r="G17" s="222">
         <f>F17</f>
         <v>141941.720305</v>
       </c>
@@ -2877,19 +2872,19 @@
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3660.8494999999998</v>
       </c>
       <c r="L17" s="25">
         <f t="shared" si="3"/>
-        <v>72641.720304999995</v>
+        <v>120515.05427499999</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1">
@@ -2907,18 +2902,18 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="151">
-        <v>959456.33722838294</v>
-      </c>
-      <c r="G18" s="161">
-        <v>500000</v>
+        <v>608812.26739283314</v>
+      </c>
+      <c r="G18" s="223">
+        <v>350000</v>
       </c>
       <c r="H18" s="152">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>459456.33722838294</v>
+        <v>258812.26739283314</v>
       </c>
       <c r="I18" s="152">
         <f t="shared" si="6"/>
-        <v>16999.88447745017</v>
+        <v>9576.0538935348268</v>
       </c>
       <c r="J18" s="152">
         <f t="shared" si="1"/>
@@ -2926,19 +2921,19 @@
       </c>
       <c r="K18" s="152">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3413.6233000000002</v>
       </c>
       <c r="L18" s="153">
         <f t="shared" si="3"/>
-        <v>67736.045687000005</v>
+        <v>112376.375285</v>
       </c>
       <c r="M18" s="153">
         <f t="shared" si="4"/>
-        <v>64620</v>
+        <v>0</v>
       </c>
       <c r="N18" s="153">
         <f t="shared" si="5"/>
-        <v>608812.26739283314</v>
+        <v>384178.31987136794</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
@@ -2958,16 +2953,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="151">
-        <v>1172976.9143317495</v>
-      </c>
-      <c r="G19" s="161"/>
+        <v>1369010.4944640244</v>
+      </c>
+      <c r="G19" s="223"/>
       <c r="H19" s="152">
         <f t="shared" si="0"/>
-        <v>1172976.9143317495</v>
+        <v>1369010.4944640244</v>
       </c>
       <c r="I19" s="152">
         <f t="shared" si="6"/>
-        <v>43400.145830274741</v>
+        <v>50653.388295168908</v>
       </c>
       <c r="J19" s="152">
         <f t="shared" si="1"/>
@@ -2975,19 +2970,19 @@
       </c>
       <c r="K19" s="152">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3936.6017999999999</v>
       </c>
       <c r="L19" s="153">
         <f t="shared" si="3"/>
-        <v>78113.434301999994</v>
+        <v>129592.81160999999</v>
       </c>
       <c r="M19" s="153">
         <f t="shared" si="4"/>
-        <v>74520</v>
+        <v>0</v>
       </c>
       <c r="N19" s="153">
         <f t="shared" si="5"/>
-        <v>1369010.4944640244</v>
+        <v>1553193.2961691935</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -3009,7 +3004,7 @@
       <c r="F20" s="17">
         <v>197243.68925499998</v>
       </c>
-      <c r="G20" s="160">
+      <c r="G20" s="222">
         <f>F20</f>
         <v>197243.68925499998</v>
       </c>
@@ -3027,19 +3022,19 @@
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5087.1544999999996</v>
       </c>
       <c r="L20" s="25">
         <f t="shared" si="3"/>
-        <v>100943.68925499999</v>
+        <v>167468.971525</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>96300</v>
+        <v>0</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1">
@@ -3059,16 +3054,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="151">
-        <v>647000.59625399474</v>
-      </c>
-      <c r="G21" s="182"/>
+        <v>812881.33862039249</v>
+      </c>
+      <c r="G21" s="224">
+        <v>145583.44</v>
+      </c>
       <c r="H21" s="152">
         <f t="shared" si="0"/>
-        <v>647000.59625399474</v>
+        <v>667297.89862039243</v>
       </c>
       <c r="I21" s="152">
         <f t="shared" si="6"/>
-        <v>23939.022061397809</v>
+        <v>24690.022248954523</v>
       </c>
       <c r="J21" s="152">
         <f t="shared" si="1"/>
@@ -3076,19 +3073,19 @@
       </c>
       <c r="K21" s="152">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3660.8494999999998</v>
       </c>
       <c r="L21" s="153">
         <f t="shared" si="3"/>
-        <v>72641.720304999995</v>
+        <v>120515.05427499999</v>
       </c>
       <c r="M21" s="153">
         <f t="shared" si="4"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="N21" s="153">
         <f t="shared" si="5"/>
-        <v>812881.33862039249</v>
+        <v>816163.82464434695</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -3110,7 +3107,7 @@
       <c r="F22" s="17">
         <v>132356.04568700001</v>
       </c>
-      <c r="G22" s="160">
+      <c r="G22" s="222">
         <f>F22</f>
         <v>132356.04568700001</v>
       </c>
@@ -3128,19 +3125,19 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3413.6233000000002</v>
       </c>
       <c r="L22" s="25">
         <f t="shared" si="3"/>
-        <v>67736.045687000005</v>
+        <v>112376.375285</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>64620</v>
+        <v>0</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
@@ -3162,7 +3159,7 @@
       <c r="F23" s="17">
         <v>152633.43430199998</v>
       </c>
-      <c r="G23" s="160">
+      <c r="G23" s="222">
         <f>F23</f>
         <v>152633.43430199998</v>
       </c>
@@ -3180,19 +3177,19 @@
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3936.6017999999999</v>
       </c>
       <c r="L23" s="25">
         <f t="shared" si="3"/>
-        <v>78113.434301999994</v>
+        <v>129592.81160999999</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>74520</v>
+        <v>0</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>152633.43430199998</v>
+        <v>133529.41340999998</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
@@ -3212,7 +3209,7 @@
       <c r="F24" s="17">
         <v>197243.68925499998</v>
       </c>
-      <c r="G24" s="160">
+      <c r="G24" s="222">
         <f>F24</f>
         <v>197243.68925499998</v>
       </c>
@@ -3230,19 +3227,19 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5087.1544999999996</v>
       </c>
       <c r="L24" s="25">
         <f t="shared" si="3"/>
-        <v>100943.68925499999</v>
+        <v>167468.971525</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>96300</v>
+        <v>0</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>197243.68925499998</v>
+        <v>172556.12602500001</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" ht="15.75" customHeight="1">
@@ -3264,8 +3261,8 @@
       <c r="F25" s="17">
         <v>141941.720305</v>
       </c>
-      <c r="G25" s="160">
-        <f t="shared" ref="G25:G26" si="7">F25</f>
+      <c r="G25" s="222">
+        <f>F25</f>
         <v>141941.720305</v>
       </c>
       <c r="H25" s="24">
@@ -3282,19 +3279,19 @@
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3660.8494999999998</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="3"/>
-        <v>72641.720304999995</v>
+        <v>120515.05427499999</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
@@ -3314,9 +3311,8 @@
       <c r="F26" s="17">
         <v>132356.04568700001</v>
       </c>
-      <c r="G26" s="160">
-        <f t="shared" si="7"/>
-        <v>132356.04568700001</v>
+      <c r="G26" s="222">
+        <v>132500</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -3328,23 +3324,23 @@
       </c>
       <c r="J26" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>143.95431299999473</v>
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3413.6233000000002</v>
       </c>
       <c r="L26" s="25">
         <f t="shared" si="3"/>
-        <v>67736.045687000005</v>
+        <v>112376.375285</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>64620</v>
+        <v>0</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>132356.04568700001</v>
+        <v>115646.04427200001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
@@ -3364,18 +3360,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="151">
-        <v>2443598.4259307226</v>
-      </c>
-      <c r="G27" s="161">
-        <v>152633.43</v>
-      </c>
-      <c r="H27" s="181">
+        <v>2528364.1350821592</v>
+      </c>
+      <c r="G27" s="223">
+        <v>152700</v>
+      </c>
+      <c r="H27" s="174">
         <f t="shared" si="0"/>
-        <v>2290964.9959307224</v>
+        <v>2375664.1350821592</v>
       </c>
       <c r="I27" s="152">
         <f t="shared" si="6"/>
-        <v>84765.704849436748</v>
+        <v>87899.572998039905</v>
       </c>
       <c r="J27" s="152">
         <f t="shared" si="1"/>
@@ -3383,19 +3379,19 @@
       </c>
       <c r="K27" s="152">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3936.6017999999999</v>
       </c>
       <c r="L27" s="153">
         <f t="shared" si="3"/>
-        <v>78113.434301999994</v>
+        <v>129592.81160999999</v>
       </c>
       <c r="M27" s="153">
         <f t="shared" si="4"/>
-        <v>74520</v>
+        <v>0</v>
       </c>
       <c r="N27" s="153">
         <f t="shared" si="5"/>
-        <v>2528364.1350821592</v>
+        <v>2597093.1214901991</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -3413,16 +3409,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>204489.60076986992</v>
-      </c>
-      <c r="G28" s="160"/>
+        <v>409299.4052533551</v>
+      </c>
+      <c r="G28" s="222"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>204489.60076986992</v>
+        <v>409299.4052533551</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="6"/>
-        <v>7566.1152284851887</v>
+        <v>15144.07799437414</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -3431,15 +3427,15 @@
       <c r="K28" s="24"/>
       <c r="L28" s="25">
         <f t="shared" si="3"/>
-        <v>100943.68925499999</v>
+        <v>167468.971525</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>96300</v>
+        <v>0</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>409299.4052533551</v>
+        <v>591912.45477272919</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1">
@@ -3459,7 +3455,7 @@
       <c r="F29" s="17">
         <v>141941.720305</v>
       </c>
-      <c r="G29" s="160">
+      <c r="G29" s="222">
         <f>F29</f>
         <v>141941.720305</v>
       </c>
@@ -3477,19 +3473,19 @@
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3660.8494999999998</v>
       </c>
       <c r="L29" s="25">
         <f t="shared" si="3"/>
-        <v>72641.720304999995</v>
+        <v>120515.05427499999</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>141941.720305</v>
+        <v>124175.90377499998</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -3512,7 +3508,7 @@
       <c r="F30" s="17">
         <v>132356.04568700001</v>
       </c>
-      <c r="G30" s="160">
+      <c r="G30" s="222">
         <f>F30</f>
         <v>132356.04568700001</v>
       </c>
@@ -3530,19 +3526,19 @@
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3413.6233000000002</v>
       </c>
       <c r="L30" s="25">
         <f t="shared" si="3"/>
-        <v>67736.045687000005</v>
+        <v>112376.375285</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>64620</v>
+        <v>0</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>132356.04568700001</v>
+        <v>115789.99858500001</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
@@ -3562,7 +3558,7 @@
       <c r="F31" s="17">
         <v>152633.43430199998</v>
       </c>
-      <c r="G31" s="160">
+      <c r="G31" s="222">
         <f>F31</f>
         <v>152633.43430199998</v>
       </c>
@@ -3580,22 +3576,22 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3936.6017999999999</v>
       </c>
       <c r="L31" s="25">
         <f t="shared" si="3"/>
-        <v>78113.434301999994</v>
+        <v>129592.81160999999</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>74520</v>
+        <v>0</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>152633.43430199998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="15.6">
+        <v>133529.41340999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -3609,149 +3605,149 @@
       </c>
       <c r="F32" s="100">
         <f>SUM(F9:F31)</f>
-        <v>10121902.394378088</v>
+        <v>10691122.144921415</v>
       </c>
       <c r="G32" s="100">
         <f>SUM(G9:G31)</f>
-        <v>3367491.3867393089</v>
+        <v>3211857.995042</v>
       </c>
       <c r="H32" s="126">
         <f>SUM(H9:H31)</f>
-        <v>6754411.0076387785</v>
+        <v>7479408.1041924143</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>249913.20728263486</v>
+        <v>276738.09985511936</v>
       </c>
       <c r="J32" s="100">
-        <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>0</v>
+        <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
+        <v>143.95431299999473</v>
       </c>
       <c r="K32" s="91">
         <f>SUM(K9:K31)</f>
-        <v>0</v>
+        <v>89999.845499999996</v>
       </c>
       <c r="L32" s="54">
         <f>SUM(L9:L31)</f>
-        <v>1886797.9300000004</v>
+        <v>3130261.1500000004</v>
       </c>
       <c r="M32" s="91">
         <f>SUM(M9:M31)</f>
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>10691122.144921415</v>
+        <v>10976263.245234534</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="185"/>
-      <c r="C34" s="185"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="185"/>
-      <c r="G34" s="185"/>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="185"/>
-      <c r="K34" s="185"/>
-      <c r="L34" s="185"/>
-      <c r="M34" s="185"/>
-      <c r="N34" s="185"/>
+      <c r="B34" s="176"/>
+      <c r="C34" s="176"/>
+      <c r="D34" s="176"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="176"/>
+      <c r="G34" s="176"/>
+      <c r="H34" s="176"/>
+      <c r="I34" s="176"/>
+      <c r="J34" s="176"/>
+      <c r="K34" s="176"/>
+      <c r="L34" s="176"/>
+      <c r="M34" s="176"/>
+      <c r="N34" s="176"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="185"/>
-      <c r="C35" s="185"/>
-      <c r="D35" s="185"/>
-      <c r="E35" s="185"/>
-      <c r="F35" s="185"/>
-      <c r="G35" s="185"/>
-      <c r="H35" s="185"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="185"/>
-      <c r="K35" s="185"/>
-      <c r="L35" s="185"/>
-      <c r="M35" s="185"/>
-      <c r="N35" s="185"/>
+      <c r="B35" s="176"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="176"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="176"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="176"/>
+      <c r="L35" s="176"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="176"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="185"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="185"/>
-      <c r="J36" s="185"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="185"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="185"/>
+      <c r="B36" s="176"/>
+      <c r="C36" s="176"/>
+      <c r="D36" s="176"/>
+      <c r="E36" s="176"/>
+      <c r="F36" s="176"/>
+      <c r="G36" s="176"/>
+      <c r="H36" s="176"/>
+      <c r="I36" s="176"/>
+      <c r="J36" s="176"/>
+      <c r="K36" s="176"/>
+      <c r="L36" s="176"/>
+      <c r="M36" s="176"/>
+      <c r="N36" s="176"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="185"/>
-      <c r="C37" s="185"/>
-      <c r="D37" s="185"/>
-      <c r="E37" s="185"/>
-      <c r="F37" s="185"/>
-      <c r="G37" s="185"/>
-      <c r="H37" s="185"/>
-      <c r="I37" s="185"/>
-      <c r="J37" s="185"/>
-      <c r="K37" s="185"/>
-      <c r="L37" s="185"/>
-      <c r="M37" s="185"/>
-      <c r="N37" s="185"/>
+      <c r="B37" s="176"/>
+      <c r="C37" s="176"/>
+      <c r="D37" s="176"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
+      <c r="G37" s="176"/>
+      <c r="H37" s="176"/>
+      <c r="I37" s="176"/>
+      <c r="J37" s="176"/>
+      <c r="K37" s="176"/>
+      <c r="L37" s="176"/>
+      <c r="M37" s="176"/>
+      <c r="N37" s="176"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="187"/>
-      <c r="B38" s="187"/>
-      <c r="C38" s="187"/>
-      <c r="D38" s="187"/>
-      <c r="E38" s="187"/>
-      <c r="F38" s="187"/>
-      <c r="G38" s="187"/>
-      <c r="H38" s="187"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="187"/>
-      <c r="L38" s="187"/>
-      <c r="M38" s="187"/>
-      <c r="N38" s="187"/>
+      <c r="A38" s="178"/>
+      <c r="B38" s="178"/>
+      <c r="C38" s="178"/>
+      <c r="D38" s="178"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="178"/>
+      <c r="G38" s="178"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+      <c r="L38" s="178"/>
+      <c r="M38" s="178"/>
+      <c r="N38" s="178"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="187"/>
-      <c r="B39" s="187"/>
-      <c r="C39" s="187"/>
-      <c r="D39" s="187"/>
-      <c r="E39" s="187"/>
-      <c r="F39" s="187"/>
-      <c r="G39" s="187"/>
-      <c r="H39" s="187"/>
-      <c r="I39" s="187"/>
-      <c r="J39" s="187"/>
-      <c r="K39" s="187"/>
-      <c r="L39" s="187"/>
-      <c r="M39" s="187"/>
-      <c r="N39" s="187"/>
+      <c r="A39" s="178"/>
+      <c r="B39" s="178"/>
+      <c r="C39" s="178"/>
+      <c r="D39" s="178"/>
+      <c r="E39" s="178"/>
+      <c r="F39" s="178"/>
+      <c r="G39" s="178"/>
+      <c r="H39" s="178"/>
+      <c r="I39" s="178"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="178"/>
+      <c r="L39" s="178"/>
+      <c r="M39" s="178"/>
+      <c r="N39" s="178"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="187"/>
-      <c r="B40" s="187"/>
-      <c r="C40" s="187"/>
-      <c r="D40" s="187"/>
-      <c r="E40" s="187"/>
-      <c r="F40" s="187"/>
-      <c r="G40" s="187"/>
-      <c r="H40" s="187"/>
-      <c r="I40" s="187"/>
-      <c r="J40" s="187"/>
-      <c r="K40" s="187"/>
-      <c r="L40" s="187"/>
-      <c r="M40" s="187"/>
-      <c r="N40" s="187"/>
+      <c r="A40" s="178"/>
+      <c r="B40" s="178"/>
+      <c r="C40" s="178"/>
+      <c r="D40" s="178"/>
+      <c r="E40" s="178"/>
+      <c r="F40" s="178"/>
+      <c r="G40" s="178"/>
+      <c r="H40" s="178"/>
+      <c r="I40" s="178"/>
+      <c r="J40" s="178"/>
+      <c r="K40" s="178"/>
+      <c r="L40" s="178"/>
+      <c r="M40" s="178"/>
+      <c r="N40" s="178"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -3772,25 +3768,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="179" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="190"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="181"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -3826,13 +3822,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -4193,7 +4189,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -4215,7 +4211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -4237,7 +4233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -4259,7 +4255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -4285,7 +4281,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -4307,7 +4303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -4329,7 +4325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -4351,7 +4347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -4373,7 +4369,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -4413,17 +4409,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K105"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4438,23 +4434,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="223"/>
-      <c r="E2" s="224"/>
-      <c r="F2" s="224"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="184"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="199">
+      <c r="E3" s="213">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="200"/>
+      <c r="F3" s="213"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -4490,7 +4486,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -4501,10 +4497,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -4533,14 +4529,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="231"/>
+      <c r="A12" s="191"/>
       <c r="B12" s="192"/>
       <c r="C12" s="192"/>
       <c r="D12" s="192"/>
       <c r="E12" s="192"/>
       <c r="F12" s="192"/>
       <c r="G12" s="192"/>
-      <c r="H12" s="232"/>
+      <c r="H12" s="193"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -4552,75 +4548,75 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="205" t="s">
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-      <c r="F14" s="205"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="205"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
+      <c r="F14" s="217"/>
+      <c r="G14" s="217"/>
+      <c r="H14" s="217"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="170" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="141"/>
-      <c r="C15" s="141"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="141"/>
-      <c r="H15" s="74">
-        <v>481237.02</v>
+      <c r="A15" s="225" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" s="226"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="226"/>
+      <c r="E15" s="226"/>
+      <c r="F15" s="226"/>
+      <c r="G15" s="226"/>
+      <c r="H15" s="129">
+        <v>311513.3</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="225" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="141"/>
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="74">
-        <v>-75794.83</v>
+      <c r="B16" s="226"/>
+      <c r="C16" s="226"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
+      <c r="F16" s="226"/>
+      <c r="G16" s="226"/>
+      <c r="H16" s="129">
+        <v>-49063.65</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="170" t="s">
+      <c r="A17" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="141"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="74">
-        <v>0.81</v>
+      <c r="B17" s="226"/>
+      <c r="C17" s="226"/>
+      <c r="D17" s="226"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="226"/>
+      <c r="G17" s="226"/>
+      <c r="H17" s="129">
+        <v>0.35</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="170" t="s">
+      <c r="A18" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="141"/>
-      <c r="C18" s="141"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="141"/>
-      <c r="G18" s="141"/>
-      <c r="H18" s="74">
+      <c r="B18" s="226"/>
+      <c r="C18" s="226"/>
+      <c r="D18" s="226"/>
+      <c r="E18" s="226"/>
+      <c r="F18" s="226"/>
+      <c r="G18" s="226"/>
+      <c r="H18" s="129">
         <f>SUM(H15:H17)</f>
-        <v>405443</v>
+        <v>262449.99999999994</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -4637,536 +4633,539 @@
       <c r="H19" s="227"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="170" t="s">
+      <c r="A20" s="225" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="141"/>
-      <c r="C20" s="141"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="141"/>
-      <c r="G20" s="141"/>
-      <c r="H20" s="74"/>
+      <c r="B20" s="226"/>
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="226"/>
+      <c r="G20" s="226"/>
+      <c r="H20" s="129"/>
     </row>
     <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="170"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="74">
+      <c r="A21" s="225"/>
+      <c r="B21" s="226"/>
+      <c r="C21" s="226"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="226"/>
+      <c r="F21" s="226"/>
+      <c r="G21" s="226"/>
+      <c r="H21" s="129">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="170"/>
-      <c r="B22" s="141"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="141"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="74">
+      <c r="A22" s="225"/>
+      <c r="B22" s="226"/>
+      <c r="C22" s="226"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="226"/>
+      <c r="G22" s="226"/>
+      <c r="H22" s="129">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="170"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="141"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="74">
+      <c r="A23" s="225"/>
+      <c r="B23" s="226"/>
+      <c r="C23" s="226"/>
+      <c r="D23" s="226"/>
+      <c r="E23" s="226"/>
+      <c r="F23" s="226"/>
+      <c r="G23" s="226"/>
+      <c r="H23" s="129">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="170" t="s">
+      <c r="A24" s="225" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="74"/>
+      <c r="B24" s="226"/>
+      <c r="C24" s="226"/>
+      <c r="D24" s="226"/>
+      <c r="E24" s="226"/>
+      <c r="F24" s="226"/>
+      <c r="G24" s="226"/>
+      <c r="H24" s="129"/>
     </row>
     <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="170" t="s">
+      <c r="A25" s="225" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="141"/>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="141"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="74"/>
+      <c r="B25" s="226"/>
+      <c r="C25" s="226"/>
+      <c r="D25" s="226"/>
+      <c r="E25" s="226"/>
+      <c r="F25" s="226"/>
+      <c r="G25" s="226"/>
+      <c r="H25" s="129"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="170" t="s">
+      <c r="A26" s="225" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="141"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="141"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="141"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="70">
+      <c r="B26" s="226"/>
+      <c r="C26" s="226"/>
+      <c r="D26" s="226"/>
+      <c r="E26" s="226"/>
+      <c r="F26" s="226"/>
+      <c r="G26" s="226"/>
+      <c r="H26" s="228">
         <f>SUM(H20:H25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="226" t="s">
+      <c r="A27" s="229" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="226"/>
-      <c r="C27" s="226"/>
-      <c r="D27" s="226"/>
-      <c r="E27" s="226"/>
-      <c r="F27" s="226"/>
-      <c r="G27" s="226"/>
-      <c r="H27" s="226"/>
+      <c r="B27" s="229"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="229"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="141" t="s">
+      <c r="A28" s="226" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="141"/>
-      <c r="C28" s="141"/>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="74">
+      <c r="B28" s="226"/>
+      <c r="C28" s="226"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="226"/>
+      <c r="F28" s="226"/>
+      <c r="G28" s="226"/>
+      <c r="H28" s="129">
         <v>32000</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="141"/>
-      <c r="B29" s="141"/>
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="74"/>
+      <c r="A29" s="226"/>
+      <c r="B29" s="226"/>
+      <c r="C29" s="226"/>
+      <c r="D29" s="226"/>
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="226"/>
+      <c r="H29" s="129"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="141"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="141"/>
-      <c r="G30" s="141"/>
-      <c r="H30" s="74">
+      <c r="B30" s="226"/>
+      <c r="C30" s="226"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="226"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="226"/>
+      <c r="H30" s="129">
         <f>SUM(H28:H29)</f>
         <v>32000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A31" s="206" t="s">
+      <c r="A31" s="230" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="206"/>
-      <c r="C31" s="206"/>
-      <c r="D31" s="206"/>
-      <c r="E31" s="206"/>
-      <c r="F31" s="206"/>
-      <c r="G31" s="206"/>
-      <c r="H31" s="206"/>
+      <c r="B31" s="230"/>
+      <c r="C31" s="230"/>
+      <c r="D31" s="230"/>
+      <c r="E31" s="230"/>
+      <c r="F31" s="230"/>
+      <c r="G31" s="230"/>
+      <c r="H31" s="230"/>
     </row>
     <row r="32" spans="1:9" hidden="1">
-      <c r="A32" s="170"/>
-      <c r="B32" s="141"/>
-      <c r="C32" s="141"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="141"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="74"/>
+      <c r="A32" s="225"/>
+      <c r="B32" s="226"/>
+      <c r="C32" s="226"/>
+      <c r="D32" s="226"/>
+      <c r="E32" s="226"/>
+      <c r="F32" s="226"/>
+      <c r="G32" s="226"/>
+      <c r="H32" s="129"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="170" t="s">
+      <c r="A33" s="225" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="171"/>
-      <c r="C33" s="141"/>
-      <c r="D33" s="141"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="141"/>
-      <c r="G33" s="141"/>
-      <c r="H33" s="233">
+      <c r="B33" s="231"/>
+      <c r="C33" s="226"/>
+      <c r="D33" s="226"/>
+      <c r="E33" s="226"/>
+      <c r="F33" s="226"/>
+      <c r="G33" s="226"/>
+      <c r="H33" s="129">
         <f>43594.41+2406.19+31655.67</f>
         <v>77656.27</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="226" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="141"/>
-      <c r="D34" s="141"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="141"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="74">
+      <c r="B34" s="226"/>
+      <c r="C34" s="226"/>
+      <c r="D34" s="226"/>
+      <c r="E34" s="226"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="226"/>
+      <c r="H34" s="129">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="141" t="s">
+      <c r="A35" s="226" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="141"/>
-      <c r="C35" s="141"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="141"/>
-      <c r="G35" s="141"/>
-      <c r="H35" s="74">
+      <c r="B35" s="226"/>
+      <c r="C35" s="226"/>
+      <c r="D35" s="226"/>
+      <c r="E35" s="226"/>
+      <c r="F35" s="226"/>
+      <c r="G35" s="226"/>
+      <c r="H35" s="129">
         <f>SUM(H32:H34)</f>
         <v>77656.27</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="206" t="s">
+      <c r="A36" s="230" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="206"/>
-      <c r="C36" s="206"/>
-      <c r="D36" s="206"/>
-      <c r="E36" s="206"/>
-      <c r="F36" s="206"/>
-      <c r="G36" s="206"/>
-      <c r="H36" s="206"/>
+      <c r="B36" s="230"/>
+      <c r="C36" s="230"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="230"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="230"/>
+      <c r="H36" s="230"/>
     </row>
     <row r="37" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A37" s="141" t="s">
-        <v>149</v>
-      </c>
-      <c r="B37" s="141"/>
-      <c r="C37" s="141"/>
-      <c r="D37" s="141"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="141"/>
-      <c r="G37" s="141"/>
-      <c r="H37" s="233">
+      <c r="A37" s="226" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="226"/>
+      <c r="C37" s="226"/>
+      <c r="D37" s="226"/>
+      <c r="E37" s="226"/>
+      <c r="F37" s="226"/>
+      <c r="G37" s="226"/>
+      <c r="H37" s="129">
         <v>2015397.65</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A38" s="141" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="141"/>
-      <c r="C38" s="141"/>
-      <c r="D38" s="141"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="141"/>
-      <c r="G38" s="141"/>
-      <c r="H38" s="74">
-        <v>1056300.97</v>
+    <row r="38" spans="1:10">
+      <c r="A38" s="232" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="226"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="129">
+        <v>63551.040000000001</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="172" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="141"/>
-      <c r="C39" s="141"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-      <c r="G39" s="141"/>
-      <c r="H39" s="233">
-        <v>63551.040000000001</v>
+      <c r="A39" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="226"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
+      <c r="G39" s="226"/>
+      <c r="H39" s="21">
+        <f>SUM(H37:H38)</f>
+        <v>2078948.69</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="141" t="s">
+      <c r="A40" s="233" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="233"/>
+      <c r="C40" s="233"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="233"/>
+      <c r="H40" s="233"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="234" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="226"/>
+      <c r="E41" s="226"/>
+      <c r="F41" s="226"/>
+      <c r="G41" s="226"/>
+      <c r="H41" s="129">
+        <v>64500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="226" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="226"/>
+      <c r="C42" s="226"/>
+      <c r="D42" s="226"/>
+      <c r="E42" s="226"/>
+      <c r="F42" s="226"/>
+      <c r="G42" s="226"/>
+      <c r="H42" s="129">
+        <v>19950.189999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="234" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="234"/>
+      <c r="C43" s="234"/>
+      <c r="D43" s="234"/>
+      <c r="E43" s="234"/>
+      <c r="F43" s="234"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="129">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="226" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="226"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="226"/>
+      <c r="E44" s="226"/>
+      <c r="F44" s="226"/>
+      <c r="G44" s="226"/>
+      <c r="H44" s="129">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="226" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" s="226"/>
+      <c r="C45" s="226"/>
+      <c r="D45" s="226"/>
+      <c r="E45" s="226"/>
+      <c r="F45" s="226"/>
+      <c r="G45" s="226"/>
+      <c r="H45" s="129">
+        <v>35250</v>
+      </c>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="234" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="226"/>
+      <c r="H46" s="129">
+        <v>243400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="226" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="141"/>
-      <c r="C40" s="141"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="145">
-        <f>SUM(H37:H39)</f>
-        <v>3135249.66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="205" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="205"/>
-      <c r="C41" s="205"/>
-      <c r="D41" s="205"/>
-      <c r="E41" s="205"/>
-      <c r="F41" s="205"/>
-      <c r="G41" s="205"/>
-      <c r="H41" s="205"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="141"/>
-      <c r="C42" s="141"/>
-      <c r="D42" s="141"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="141"/>
-      <c r="G42" s="141"/>
-      <c r="H42" s="233">
-        <v>64500</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="141" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="141"/>
-      <c r="C43" s="141"/>
-      <c r="D43" s="141"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="141"/>
-      <c r="G43" s="141"/>
-      <c r="H43" s="233">
-        <v>19950.189999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="81" t="s">
+      <c r="B47" s="226"/>
+      <c r="C47" s="226"/>
+      <c r="D47" s="226"/>
+      <c r="E47" s="226"/>
+      <c r="F47" s="226"/>
+      <c r="G47" s="226"/>
+      <c r="H47" s="228">
+        <f>SUM(H41:H46)</f>
+        <v>478100.19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="233" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="233"/>
+      <c r="C48" s="233"/>
+      <c r="D48" s="233"/>
+      <c r="E48" s="233"/>
+      <c r="F48" s="233"/>
+      <c r="G48" s="233"/>
+      <c r="H48" s="233"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="226" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="226"/>
+      <c r="C49" s="226"/>
+      <c r="D49" s="226"/>
+      <c r="E49" s="226"/>
+      <c r="F49" s="226"/>
+      <c r="G49" s="226"/>
+      <c r="H49" s="129">
+        <v>148100</v>
+      </c>
+      <c r="J49" t="s">
         <v>148</v>
       </c>
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="74">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="141" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="141"/>
-      <c r="C45" s="141"/>
-      <c r="D45" s="141"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="141"/>
-      <c r="G45" s="141"/>
-      <c r="H45" s="74">
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="141" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="141"/>
-      <c r="C46" s="141"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="141"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="233">
-        <v>35250</v>
-      </c>
-      <c r="J46" s="184" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="81" t="s">
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="226" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="226"/>
+      <c r="C50" s="226"/>
+      <c r="D50" s="226"/>
+      <c r="E50" s="226"/>
+      <c r="F50" s="226"/>
+      <c r="G50" s="226"/>
+      <c r="H50" s="129">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="226"/>
+      <c r="B51" s="226"/>
+      <c r="C51" s="226"/>
+      <c r="D51" s="226"/>
+      <c r="E51" s="226"/>
+      <c r="F51" s="226"/>
+      <c r="G51" s="226"/>
+      <c r="H51" s="129"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="226" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="226"/>
+      <c r="C52" s="226"/>
+      <c r="D52" s="226"/>
+      <c r="E52" s="226"/>
+      <c r="F52" s="226"/>
+      <c r="G52" s="226"/>
+      <c r="H52" s="235">
+        <f>SUM(H49:H51)</f>
+        <v>178100</v>
+      </c>
+      <c r="K52" s="7"/>
+    </row>
+    <row r="53" spans="1:11" s="6" customFormat="1">
+      <c r="A53" s="236" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="237"/>
+      <c r="C53" s="237"/>
+      <c r="D53" s="237"/>
+      <c r="E53" s="237"/>
+      <c r="F53" s="237"/>
+      <c r="G53" s="237"/>
+      <c r="H53" s="238"/>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="234" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="234"/>
+      <c r="C54" s="234"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="234"/>
+      <c r="F54" s="234"/>
+      <c r="G54" s="234"/>
+      <c r="H54" s="228">
+        <v>23006</v>
+      </c>
+      <c r="I54" s="60"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1">
+      <c r="A55" s="234" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="234"/>
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="234"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="228">
+        <f>SUM(H54)</f>
+        <v>23006</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="233" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" s="233"/>
+      <c r="C56" s="233"/>
+      <c r="D56" s="233"/>
+      <c r="E56" s="233"/>
+      <c r="F56" s="233"/>
+      <c r="G56" s="233"/>
+      <c r="H56" s="233"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1">
+      <c r="A57" s="234" t="s">
         <v>157</v>
       </c>
-      <c r="B47" s="141"/>
-      <c r="C47" s="141"/>
-      <c r="D47" s="141"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="141"/>
-      <c r="G47" s="141"/>
-      <c r="H47" s="74">
-        <f>180000+85000</f>
-        <v>265000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="141"/>
-      <c r="B48" s="141"/>
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-      <c r="F48" s="141"/>
-      <c r="G48" s="141"/>
-      <c r="H48" s="70">
-        <f>SUM(H42:H47)</f>
-        <v>484700.19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="205" t="s">
-        <v>139</v>
-      </c>
-      <c r="B49" s="205"/>
-      <c r="C49" s="205"/>
-      <c r="D49" s="205"/>
-      <c r="E49" s="205"/>
-      <c r="F49" s="205"/>
-      <c r="G49" s="205"/>
-      <c r="H49" s="205"/>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="141" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="141"/>
-      <c r="C50" s="141"/>
-      <c r="D50" s="141"/>
-      <c r="E50" s="141"/>
-      <c r="F50" s="141"/>
-      <c r="G50" s="141"/>
-      <c r="H50" s="74">
-        <v>148100</v>
-      </c>
-      <c r="J50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="141" t="s">
-        <v>121</v>
-      </c>
-      <c r="B51" s="141"/>
-      <c r="C51" s="141"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="141"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="74">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="141"/>
-      <c r="B52" s="141"/>
-      <c r="C52" s="141"/>
-      <c r="D52" s="141"/>
-      <c r="E52" s="141"/>
-      <c r="F52" s="141"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="74"/>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="141" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="141"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="141"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="173">
-        <f>SUM(H50:H52)</f>
-        <v>178100</v>
-      </c>
-      <c r="K53" s="7"/>
-    </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="207" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="208"/>
-      <c r="C54" s="208"/>
-      <c r="D54" s="208"/>
-      <c r="E54" s="208"/>
-      <c r="F54" s="208"/>
-      <c r="G54" s="208"/>
-      <c r="H54" s="209"/>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="81"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="234">
-        <v>23006</v>
-      </c>
-      <c r="I55" s="60"/>
-    </row>
-    <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="81"/>
-      <c r="C56" s="81"/>
-      <c r="D56" s="81"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="70">
-        <f>SUM(H55)</f>
-        <v>23006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="205" t="s">
-        <v>141</v>
-      </c>
-      <c r="B57" s="205"/>
-      <c r="C57" s="205"/>
-      <c r="D57" s="205"/>
-      <c r="E57" s="205"/>
-      <c r="F57" s="205"/>
-      <c r="G57" s="205"/>
-      <c r="H57" s="205"/>
+      <c r="B57" s="234"/>
+      <c r="C57" s="234"/>
+      <c r="D57" s="234"/>
+      <c r="E57" s="234"/>
+      <c r="F57" s="234"/>
+      <c r="G57" s="234"/>
+      <c r="H57" s="228">
+        <v>90000</v>
+      </c>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="81"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="70"/>
+      <c r="A58" s="234"/>
+      <c r="B58" s="234"/>
+      <c r="C58" s="234"/>
+      <c r="D58" s="234"/>
+      <c r="E58" s="234"/>
+      <c r="F58" s="234"/>
+      <c r="G58" s="234"/>
+      <c r="H58" s="228"/>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="81"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="81"/>
-      <c r="D59" s="81"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="70"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="81"/>
+      <c r="A59" s="234"/>
+      <c r="B59" s="234"/>
+      <c r="C59" s="234"/>
+      <c r="D59" s="234"/>
+      <c r="E59" s="234"/>
+      <c r="F59" s="234"/>
+      <c r="G59" s="234"/>
+      <c r="H59" s="228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A60" s="81" t="s">
+        <v>76</v>
+      </c>
       <c r="B60" s="81"/>
       <c r="C60" s="81"/>
       <c r="D60" s="81"/>
@@ -5174,279 +5173,274 @@
       <c r="F60" s="81"/>
       <c r="G60" s="81"/>
       <c r="H60" s="70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A61" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="70">
-        <f>SUM(H58:H60)</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="60"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="207"/>
-      <c r="B62" s="208"/>
-      <c r="C62" s="208"/>
-      <c r="D62" s="208"/>
-      <c r="E62" s="208"/>
-      <c r="F62" s="208"/>
-      <c r="G62" s="208"/>
-      <c r="H62" s="209"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A63" s="82"/>
-      <c r="B63" s="83"/>
-      <c r="C63" s="83"/>
-      <c r="D63" s="83"/>
-      <c r="E63" s="83"/>
-      <c r="F63" s="83"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A64" s="163"/>
-      <c r="B64" s="164"/>
-      <c r="C64" s="164"/>
-      <c r="D64" s="164"/>
-      <c r="E64" s="164"/>
-      <c r="F64" s="164"/>
-      <c r="G64" s="164"/>
-      <c r="H64" s="165">
+        <f>SUM(H57:H59)</f>
+        <v>90000</v>
+      </c>
+      <c r="I60" s="60"/>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A61" s="218"/>
+      <c r="B61" s="219"/>
+      <c r="C61" s="219"/>
+      <c r="D61" s="219"/>
+      <c r="E61" s="219"/>
+      <c r="F61" s="219"/>
+      <c r="G61" s="219"/>
+      <c r="H61" s="220"/>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A62" s="82"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="83"/>
+      <c r="E62" s="83"/>
+      <c r="F62" s="83"/>
+      <c r="G62" s="83"/>
+      <c r="H62" s="160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A63" s="161"/>
+      <c r="B63" s="162"/>
+      <c r="C63" s="162"/>
+      <c r="D63" s="162"/>
+      <c r="E63" s="162"/>
+      <c r="F63" s="162"/>
+      <c r="G63" s="162"/>
+      <c r="H63" s="163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A64" s="164"/>
+      <c r="B64" s="165"/>
+      <c r="C64" s="165"/>
+      <c r="D64" s="165"/>
+      <c r="E64" s="165"/>
+      <c r="F64" s="165"/>
+      <c r="G64" s="165"/>
+      <c r="H64" s="160">
+        <f>H62+H63</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A65" s="166"/>
-      <c r="B65" s="167"/>
-      <c r="C65" s="167"/>
-      <c r="D65" s="167"/>
-      <c r="E65" s="167"/>
-      <c r="F65" s="167"/>
-      <c r="G65" s="167"/>
-      <c r="H65" s="162">
-        <f>H63+H64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A66" s="218" t="s">
+      <c r="A65" s="199" t="s">
         <v>84</v>
       </c>
-      <c r="B66" s="219"/>
-      <c r="C66" s="219"/>
-      <c r="D66" s="219"/>
-      <c r="E66" s="219"/>
-      <c r="F66" s="219"/>
-      <c r="G66" s="219"/>
-      <c r="H66" s="168">
-        <f>H61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A67" s="221"/>
-      <c r="B67" s="221"/>
-      <c r="C67" s="221"/>
-      <c r="D67" s="221"/>
-      <c r="E67" s="221"/>
-      <c r="F67" s="221"/>
-      <c r="G67" s="221"/>
-      <c r="H67" s="221"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A68" s="222"/>
-      <c r="B68" s="222"/>
-      <c r="C68" s="222"/>
-      <c r="D68" s="222"/>
-      <c r="E68" s="222"/>
-      <c r="F68" s="222"/>
-      <c r="G68" s="222"/>
-      <c r="H68" s="222"/>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A69" s="220" t="s">
+      <c r="B65" s="200"/>
+      <c r="C65" s="200"/>
+      <c r="D65" s="200"/>
+      <c r="E65" s="200"/>
+      <c r="F65" s="200"/>
+      <c r="G65" s="200"/>
+      <c r="H65" s="166">
+        <f>H60</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="204"/>
+      <c r="B66" s="204"/>
+      <c r="C66" s="204"/>
+      <c r="D66" s="204"/>
+      <c r="E66" s="204"/>
+      <c r="F66" s="204"/>
+      <c r="G66" s="204"/>
+      <c r="H66" s="204"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A67" s="205"/>
+      <c r="B67" s="205"/>
+      <c r="C67" s="205"/>
+      <c r="D67" s="205"/>
+      <c r="E67" s="205"/>
+      <c r="F67" s="205"/>
+      <c r="G67" s="205"/>
+      <c r="H67" s="205"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A68" s="203" t="s">
         <v>86</v>
       </c>
-      <c r="B69" s="220"/>
-      <c r="C69" s="220"/>
-      <c r="D69" s="220"/>
-      <c r="E69" s="220"/>
-      <c r="F69" s="220"/>
-      <c r="G69" s="220"/>
-      <c r="H69" s="169"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A70" s="228"/>
-      <c r="B70" s="229"/>
-      <c r="C70" s="229"/>
-      <c r="D70" s="229"/>
-      <c r="E70" s="229"/>
-      <c r="F70" s="229"/>
-      <c r="G70" s="230"/>
-      <c r="H70" s="74"/>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A71" s="131" t="s">
+      <c r="B68" s="203"/>
+      <c r="C68" s="203"/>
+      <c r="D68" s="203"/>
+      <c r="E68" s="203"/>
+      <c r="F68" s="203"/>
+      <c r="G68" s="203"/>
+      <c r="H68" s="167"/>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A69" s="188"/>
+      <c r="B69" s="189"/>
+      <c r="C69" s="189"/>
+      <c r="D69" s="189"/>
+      <c r="E69" s="189"/>
+      <c r="F69" s="189"/>
+      <c r="G69" s="190"/>
+      <c r="H69" s="74"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A70" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="81"/>
-      <c r="G71" s="81"/>
-      <c r="H71" s="70">
-        <f>SUM(H70:H70)</f>
-        <v>0</v>
-      </c>
+      <c r="B70" s="81"/>
+      <c r="C70" s="81"/>
+      <c r="D70" s="81"/>
+      <c r="E70" s="81"/>
+      <c r="F70" s="81"/>
+      <c r="G70" s="81"/>
+      <c r="H70" s="70">
+        <f>SUM(H69:H69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="132"/>
+      <c r="B71" s="132"/>
+      <c r="C71" s="132"/>
+      <c r="D71" s="132"/>
+      <c r="E71" s="132"/>
+      <c r="F71" s="132"/>
+      <c r="G71" s="132"/>
+      <c r="H71" s="133"/>
     </row>
     <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="132"/>
-      <c r="B72" s="132"/>
-      <c r="C72" s="132"/>
-      <c r="D72" s="132"/>
-      <c r="E72" s="132"/>
-      <c r="F72" s="132"/>
-      <c r="G72" s="132"/>
-      <c r="H72" s="133"/>
+      <c r="A72" s="201" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="202"/>
+      <c r="C72" s="202"/>
+      <c r="D72" s="202"/>
+      <c r="E72" s="202"/>
+      <c r="F72" s="202"/>
+      <c r="G72" s="202"/>
+      <c r="H72" s="134">
+        <f>H70</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="201" t="s">
-        <v>85</v>
-      </c>
-      <c r="B73" s="202"/>
-      <c r="C73" s="202"/>
-      <c r="D73" s="202"/>
-      <c r="E73" s="202"/>
-      <c r="F73" s="202"/>
-      <c r="G73" s="202"/>
-      <c r="H73" s="134">
-        <f>H71</f>
-        <v>0</v>
-      </c>
+      <c r="A73" s="185" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="186"/>
+      <c r="C73" s="186"/>
+      <c r="D73" s="186"/>
+      <c r="E73" s="186"/>
+      <c r="F73" s="186"/>
+      <c r="G73" s="187"/>
+      <c r="H73" s="134"/>
     </row>
     <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A74" s="213" t="s">
-        <v>91</v>
-      </c>
-      <c r="B74" s="214"/>
-      <c r="C74" s="214"/>
-      <c r="D74" s="214"/>
-      <c r="E74" s="214"/>
-      <c r="F74" s="214"/>
-      <c r="G74" s="215"/>
+      <c r="A74" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="186"/>
+      <c r="C74" s="186"/>
+      <c r="D74" s="186"/>
+      <c r="E74" s="186"/>
+      <c r="F74" s="186"/>
+      <c r="G74" s="187"/>
       <c r="H74" s="134"/>
     </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="213" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="214"/>
-      <c r="C75" s="214"/>
-      <c r="D75" s="214"/>
-      <c r="E75" s="214"/>
-      <c r="F75" s="214"/>
-      <c r="G75" s="215"/>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="201" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" s="202"/>
+      <c r="C75" s="202"/>
+      <c r="D75" s="202"/>
+      <c r="E75" s="202"/>
+      <c r="F75" s="202"/>
+      <c r="G75" s="202"/>
       <c r="H75" s="134">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="18">
-      <c r="A76" s="201" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" s="202"/>
-      <c r="C76" s="202"/>
-      <c r="D76" s="202"/>
-      <c r="E76" s="202"/>
-      <c r="F76" s="202"/>
-      <c r="G76" s="202"/>
-      <c r="H76" s="134">
-        <f>H30+H40+H48+H53+H56+H35+H18+H26</f>
-        <v>4336155.12</v>
-      </c>
-      <c r="J76" s="183"/>
-      <c r="K76" s="146"/>
-    </row>
-    <row r="77" spans="1:11" ht="18">
-      <c r="A77" s="210" t="s">
+        <f>H30+H39+H47+H52+H55+H35+H18+H26</f>
+        <v>3130261.15</v>
+      </c>
+      <c r="J75" s="175"/>
+      <c r="K75" s="146"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75">
+      <c r="A76" s="194" t="s">
         <v>126</v>
       </c>
-      <c r="B77" s="211"/>
-      <c r="C77" s="211"/>
-      <c r="D77" s="211"/>
-      <c r="E77" s="211"/>
-      <c r="F77" s="211"/>
-      <c r="G77" s="212"/>
-      <c r="H77" s="135">
-        <f>H74+H76</f>
-        <v>4336155.12</v>
-      </c>
-      <c r="I77" s="130"/>
-      <c r="J77" s="191"/>
-      <c r="K77" s="191"/>
-    </row>
-    <row r="78" spans="1:11" ht="18">
-      <c r="A78" s="210" t="s">
+      <c r="B76" s="195"/>
+      <c r="C76" s="195"/>
+      <c r="D76" s="195"/>
+      <c r="E76" s="195"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="196"/>
+      <c r="H76" s="135">
+        <f>H73+H75</f>
+        <v>3130261.15</v>
+      </c>
+      <c r="I76" s="130"/>
+      <c r="J76" s="206"/>
+      <c r="K76" s="206"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75">
+      <c r="A77" s="194" t="s">
         <v>97</v>
       </c>
-      <c r="B78" s="211"/>
-      <c r="C78" s="211"/>
-      <c r="D78" s="211"/>
-      <c r="E78" s="211"/>
-      <c r="F78" s="211"/>
-      <c r="G78" s="212"/>
-      <c r="H78" s="136">
-        <f>H75+H73</f>
-        <v>1800000</v>
-      </c>
-      <c r="J78" s="146"/>
-    </row>
-    <row r="79" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A79" s="216" t="s">
+      <c r="B77" s="195"/>
+      <c r="C77" s="195"/>
+      <c r="D77" s="195"/>
+      <c r="E77" s="195"/>
+      <c r="F77" s="195"/>
+      <c r="G77" s="196"/>
+      <c r="H77" s="136">
+        <f>H74+H72</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="146"/>
+    </row>
+    <row r="78" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A78" s="197" t="s">
         <v>87</v>
       </c>
-      <c r="B79" s="217"/>
-      <c r="C79" s="217"/>
-      <c r="D79" s="217"/>
-      <c r="E79" s="217"/>
-      <c r="F79" s="217"/>
-      <c r="G79" s="217"/>
-      <c r="H79" s="137">
-        <f>H76+H73</f>
-        <v>4336155.12</v>
+      <c r="B78" s="198"/>
+      <c r="C78" s="198"/>
+      <c r="D78" s="198"/>
+      <c r="E78" s="198"/>
+      <c r="F78" s="198"/>
+      <c r="G78" s="198"/>
+      <c r="H78" s="137">
+        <f>H75+H72</f>
+        <v>3130261.15</v>
+      </c>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
+      <c r="A79" s="215" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" s="216"/>
+      <c r="C79" s="216"/>
+      <c r="D79" s="216"/>
+      <c r="E79" s="216"/>
+      <c r="F79" s="216"/>
+      <c r="G79" s="216"/>
+      <c r="H79" s="138">
+        <f>H64</f>
+        <v>0</v>
       </c>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:11" ht="18" hidden="1">
-      <c r="A80" s="203" t="s">
-        <v>17</v>
-      </c>
-      <c r="B80" s="204"/>
-      <c r="C80" s="204"/>
-      <c r="D80" s="204"/>
-      <c r="E80" s="204"/>
-      <c r="F80" s="204"/>
-      <c r="G80" s="204"/>
-      <c r="H80" s="138">
-        <f>H65</f>
-        <v>0</v>
-      </c>
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
+      <c r="A80" s="139"/>
+      <c r="B80" s="139"/>
+      <c r="C80" s="139"/>
+      <c r="D80" s="139"/>
+      <c r="E80" s="139"/>
+      <c r="F80" s="139"/>
+      <c r="G80" s="139"/>
+      <c r="H80" s="140"/>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:11" ht="18" hidden="1">
+    <row r="81" spans="1:11" ht="18.75" hidden="1">
       <c r="A81" s="139"/>
       <c r="B81" s="139"/>
       <c r="C81" s="139"/>
@@ -5457,7 +5451,7 @@
       <c r="H81" s="140"/>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:11" ht="18" hidden="1">
+    <row r="82" spans="1:11" ht="18.75" hidden="1">
       <c r="A82" s="139"/>
       <c r="B82" s="139"/>
       <c r="C82" s="139"/>
@@ -5468,71 +5462,75 @@
       <c r="H82" s="140"/>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="18" hidden="1">
-      <c r="A83" s="139"/>
-      <c r="B83" s="139"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="139"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="140"/>
-      <c r="J83" s="7"/>
-    </row>
-    <row r="84" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A84" s="141"/>
-      <c r="B84" s="141"/>
-      <c r="C84" s="141"/>
-      <c r="D84" s="141"/>
-      <c r="E84" s="141"/>
-      <c r="F84" s="141"/>
-      <c r="G84" s="141"/>
-      <c r="H84" s="141"/>
-    </row>
-    <row r="85" spans="1:11" ht="18">
-      <c r="A85" s="196" t="s">
+    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A83" s="141"/>
+      <c r="B83" s="141"/>
+      <c r="C83" s="141"/>
+      <c r="D83" s="141"/>
+      <c r="E83" s="141"/>
+      <c r="F83" s="141"/>
+      <c r="G83" s="141"/>
+      <c r="H83" s="141"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75">
+      <c r="A84" s="210" t="s">
         <v>10</v>
       </c>
-      <c r="B85" s="197"/>
-      <c r="C85" s="197"/>
-      <c r="D85" s="197"/>
-      <c r="E85" s="197"/>
-      <c r="F85" s="197"/>
-      <c r="G85" s="197"/>
-      <c r="H85" s="198"/>
-    </row>
-    <row r="86" spans="1:11" ht="18">
-      <c r="A86" s="142" t="s">
+      <c r="B84" s="211"/>
+      <c r="C84" s="211"/>
+      <c r="D84" s="211"/>
+      <c r="E84" s="211"/>
+      <c r="F84" s="211"/>
+      <c r="G84" s="211"/>
+      <c r="H84" s="212"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75">
+      <c r="A85" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="B86" s="143"/>
-      <c r="C86" s="143"/>
-      <c r="D86" s="143"/>
-      <c r="E86" s="143"/>
-      <c r="F86" s="143"/>
-      <c r="G86" s="143"/>
-      <c r="H86" s="144">
-        <v>4583896.9266090551</v>
+      <c r="B85" s="143"/>
+      <c r="C85" s="143"/>
+      <c r="D85" s="143"/>
+      <c r="E85" s="143"/>
+      <c r="F85" s="143"/>
+      <c r="G85" s="143"/>
+      <c r="H85" s="144">
+        <v>4747227.3433483643</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="B86" s="83"/>
+      <c r="C86" s="83"/>
+      <c r="D86" s="83"/>
+      <c r="E86" s="83"/>
+      <c r="F86" s="83"/>
+      <c r="G86" s="83"/>
+      <c r="H86" s="145">
+        <f>Planilla!G32</f>
+        <v>3211857.995042</v>
       </c>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="B87" s="83"/>
-      <c r="C87" s="83"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="83"/>
-      <c r="F87" s="83"/>
-      <c r="G87" s="83"/>
-      <c r="H87" s="145">
-        <f>Planilla!G32</f>
-        <v>3367491.3867393089</v>
+      <c r="A87" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B87" s="80"/>
+      <c r="C87" s="80"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="69">
+        <f>-(H78)</f>
+        <v>-3130261.15</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="79" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="B88" s="80"/>
       <c r="C88" s="80"/>
@@ -5541,129 +5539,122 @@
       <c r="F88" s="80"/>
       <c r="G88" s="80"/>
       <c r="H88" s="69">
-        <f>-(H79)</f>
-        <v>-4336155.12</v>
-      </c>
+        <f>-H65</f>
+        <v>-90000</v>
+      </c>
+      <c r="K88" s="6"/>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="B89" s="80"/>
+        <v>73</v>
+      </c>
+      <c r="B89" s="80" t="s">
+        <v>118</v>
+      </c>
       <c r="C89" s="80"/>
       <c r="D89" s="80"/>
       <c r="E89" s="80"/>
       <c r="F89" s="80"/>
       <c r="G89" s="80"/>
-      <c r="H89" s="69">
-        <f>-H66</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="6"/>
+      <c r="H89" s="125">
+        <f>170000-H90</f>
+        <v>133680</v>
+      </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="B90" s="80" t="s">
-        <v>118</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B90" s="80"/>
       <c r="C90" s="80"/>
       <c r="D90" s="80"/>
       <c r="E90" s="80"/>
       <c r="F90" s="80"/>
       <c r="G90" s="80"/>
       <c r="H90" s="125">
-        <v>115393.04</v>
-      </c>
+        <v>36320</v>
+      </c>
+      <c r="I90" s="146"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="B91" s="80"/>
-      <c r="C91" s="80"/>
-      <c r="D91" s="80"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="125">
-        <v>54606.96</v>
-      </c>
-      <c r="I91" s="146"/>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="12" t="s">
+      <c r="A91" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B92" s="84"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="99">
-        <f>-{5402}</f>
-        <v>-5402</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="18">
-      <c r="A93" s="22" t="s">
+      <c r="B91" s="84"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="99"/>
+    </row>
+    <row r="92" spans="1:11" ht="18.75">
+      <c r="A92" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="85">
-        <f>SUM(H86:H92)</f>
-        <v>3779831.193348364</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="15" thickBot="1"/>
-    <row r="95" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A95" s="193" t="s">
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="85">
+        <f>SUM(H85:H91)</f>
+        <v>4908824.1883903649</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="94" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A94" s="207" t="s">
         <v>101</v>
       </c>
-      <c r="B95" s="194"/>
-      <c r="C95" s="194"/>
-      <c r="D95" s="194"/>
-      <c r="E95" s="194"/>
-      <c r="F95" s="194"/>
-      <c r="G95" s="194"/>
-      <c r="H95" s="195"/>
-    </row>
-    <row r="96" spans="1:11" ht="15.6">
-      <c r="A96" s="88" t="s">
+      <c r="B94" s="208"/>
+      <c r="C94" s="208"/>
+      <c r="D94" s="208"/>
+      <c r="E94" s="208"/>
+      <c r="F94" s="208"/>
+      <c r="G94" s="208"/>
+      <c r="H94" s="209"/>
+    </row>
+    <row r="95" spans="1:11" ht="15.75">
+      <c r="A95" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B96" s="88"/>
-      <c r="C96" s="88"/>
-      <c r="D96" s="88"/>
-      <c r="E96" s="88"/>
-      <c r="F96" s="88"/>
-      <c r="G96" s="88"/>
-      <c r="H96" s="89">
-        <v>0</v>
-      </c>
+      <c r="B95" s="88"/>
+      <c r="C95" s="88"/>
+      <c r="D95" s="88"/>
+      <c r="E95" s="88"/>
+      <c r="F95" s="88"/>
+      <c r="G95" s="88"/>
+      <c r="H95" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B96" s="92"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="129"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="B97" s="92"/>
-      <c r="C97" s="4"/>
+      <c r="A97" s="61"/>
+      <c r="B97" s="98"/>
+      <c r="C97" s="61"/>
       <c r="D97" s="61"/>
       <c r="E97" s="61"/>
       <c r="F97" s="61"/>
       <c r="G97" s="61"/>
-      <c r="H97" s="129"/>
+      <c r="H97" s="21"/>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="61"/>
-      <c r="B98" s="98"/>
+      <c r="B98" s="61"/>
       <c r="C98" s="61"/>
       <c r="D98" s="61"/>
       <c r="E98" s="61"/>
@@ -5672,29 +5663,29 @@
       <c r="H98" s="21"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="61"/>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="21"/>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="86" t="s">
+      <c r="A99" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B100" s="86"/>
-      <c r="C100" s="86"/>
-      <c r="D100" s="86"/>
-      <c r="E100" s="86"/>
-      <c r="F100" s="86"/>
-      <c r="G100" s="86"/>
-      <c r="H100" s="87">
-        <f>SUM(H96:H99)</f>
-        <v>0</v>
-      </c>
+      <c r="B99" s="86"/>
+      <c r="C99" s="86"/>
+      <c r="D99" s="86"/>
+      <c r="E99" s="86"/>
+      <c r="F99" s="86"/>
+      <c r="G99" s="86"/>
+      <c r="H99" s="87">
+        <f>SUM(H95:H98)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" hidden="1">
+      <c r="A102" s="192"/>
+      <c r="B102" s="192"/>
+      <c r="C102" s="192"/>
+      <c r="D102" s="192"/>
+      <c r="E102" s="192"/>
+      <c r="F102" s="192"/>
+      <c r="G102" s="192"/>
+      <c r="H102" s="192"/>
     </row>
     <row r="103" spans="1:8" hidden="1">
       <c r="A103" s="192"/>
@@ -5726,47 +5717,37 @@
       <c r="G105" s="192"/>
       <c r="H105" s="192"/>
     </row>
-    <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="192"/>
-      <c r="B106" s="192"/>
-      <c r="C106" s="192"/>
-      <c r="D106" s="192"/>
-      <c r="E106" s="192"/>
-      <c r="F106" s="192"/>
-      <c r="G106" s="192"/>
-      <c r="H106" s="192"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A102:H105"/>
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A66:H67"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A67:H68"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="A103:H106"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A74:G74"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
